--- a/docs/spec/ARM.xlsx
+++ b/docs/spec/ARM.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\EitanKrimer\Documents\university\ADSS\ADSS_Group_Y\docs\spec\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\taoma\Downloads\ADSS_Group_Y\docs\spec\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9812C38-BE7C-4DB9-8F33-28540CD5CE3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C6ADC19-3E30-42F8-8A0A-C1D87F865897}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-60" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="39">
   <si>
     <t>ID</t>
   </si>
@@ -874,6 +874,12 @@
   </si>
   <si>
     <t>???</t>
+  </si>
+  <si>
+    <t>priority</t>
+  </si>
+  <si>
+    <t>First</t>
   </si>
 </sst>
 </file>
@@ -884,7 +890,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -903,7 +909,7 @@
     <font>
       <sz val="16"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -1099,7 +1105,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
@@ -1107,22 +1113,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1131,8 +1125,8 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1143,8 +1137,17 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1435,80 +1438,85 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L55"/>
-  <sheetFormatPr defaultRowHeight="21" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.09765625" defaultRowHeight="20.399999999999999" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="2"/>
-    <col min="2" max="2" width="15.42578125" style="2" customWidth="1"/>
+    <col min="1" max="1" width="9.09765625" style="2"/>
+    <col min="2" max="2" width="15.3984375" style="2" customWidth="1"/>
     <col min="3" max="3" width="10" style="2" customWidth="1"/>
-    <col min="4" max="4" width="43.5703125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="12.140625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="9.140625" style="2"/>
-    <col min="7" max="7" width="26.28515625" style="2" customWidth="1"/>
-    <col min="8" max="10" width="9.140625" style="2"/>
-    <col min="11" max="11" width="33.7109375" style="2" customWidth="1"/>
-    <col min="12" max="12" width="46.5703125" style="2" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="2"/>
+    <col min="4" max="4" width="43.59765625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="12.09765625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="9.09765625" style="2"/>
+    <col min="7" max="8" width="26.296875" style="2" customWidth="1"/>
+    <col min="9" max="10" width="9.09765625" style="2"/>
+    <col min="11" max="11" width="33.69921875" style="2" customWidth="1"/>
+    <col min="12" max="12" width="46.59765625" style="2" customWidth="1"/>
+    <col min="13" max="16384" width="9.09765625" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="11" t="s">
         <v>5</v>
       </c>
+      <c r="H1" s="11" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="5"/>
-      <c r="B2" s="5"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="J2" s="12" t="s">
+      <c r="A2" s="12"/>
+      <c r="B2" s="12"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="12"/>
+      <c r="G2" s="12"/>
+      <c r="H2" s="12"/>
+      <c r="J2" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="K2" s="13"/>
-      <c r="L2" s="14"/>
-    </row>
-    <row r="3" spans="1:12" ht="60.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="7">
+      <c r="K2" s="9"/>
+      <c r="L2" s="10"/>
+    </row>
+    <row r="3" spans="1:12" ht="61.2" x14ac:dyDescent="0.25">
+      <c r="A3" s="3">
         <v>1</v>
       </c>
-      <c r="B3" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" s="7" t="s">
+      <c r="B3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="G3" s="3" t="s">
         <v>15</v>
       </c>
+      <c r="H3" s="3"/>
       <c r="J3" s="1" t="s">
         <v>0</v>
       </c>
@@ -1520,28 +1528,29 @@
       </c>
     </row>
     <row r="4" spans="1:12" ht="135" x14ac:dyDescent="0.25">
-      <c r="A4" s="7">
+      <c r="A4" s="3">
         <f>A3+1</f>
         <v>2</v>
       </c>
-      <c r="B4" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" s="7" t="s">
+      <c r="B4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E4" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="F4" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="G4" s="3" t="s">
         <v>15</v>
       </c>
+      <c r="H4" s="3"/>
       <c r="J4" s="1">
         <v>1</v>
       </c>
@@ -1552,1139 +1561,1192 @@
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="162" x14ac:dyDescent="0.25">
-      <c r="A5" s="7">
+    <row r="5" spans="1:12" ht="122.4" x14ac:dyDescent="0.25">
+      <c r="A5" s="3">
         <f>A4+1</f>
         <v>3</v>
       </c>
-      <c r="B5" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" s="7" t="s">
+      <c r="B5" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="E5" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="F5" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G5" s="7" t="s">
+      <c r="G5" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J5" s="9">
+      <c r="H5" s="3"/>
+      <c r="J5" s="5">
         <f>J4+1</f>
         <v>2</v>
       </c>
-      <c r="K5" s="7" t="s">
+      <c r="K5" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="L5" s="9" t="s">
+      <c r="L5" s="5" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="141.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="7">
+    <row r="6" spans="1:12" ht="142.80000000000001" x14ac:dyDescent="0.25">
+      <c r="A6" s="3">
         <f t="shared" ref="A6:A19" si="0">A5+1</f>
         <v>4</v>
       </c>
-      <c r="B6" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" s="7" t="s">
+      <c r="B6" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="E6" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="F6" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G6" s="7" t="s">
+      <c r="G6" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J6" s="9">
+      <c r="H6" s="3"/>
+      <c r="J6" s="5">
         <f t="shared" ref="J6:J19" si="1">J5+1</f>
         <v>3</v>
       </c>
-      <c r="K6" s="11" t="s">
+      <c r="K6" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="L6" s="9" t="s">
+      <c r="L6" s="5" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="147" x14ac:dyDescent="0.25">
-      <c r="A7" s="7">
+    <row r="7" spans="1:12" ht="142.80000000000001" x14ac:dyDescent="0.25">
+      <c r="A7" s="3">
         <f>A6+1</f>
         <v>5</v>
       </c>
-      <c r="B7" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C7" s="7" t="s">
+      <c r="B7" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="E7" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="F7" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G7" s="7" t="s">
+      <c r="G7" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J7" s="9">
+      <c r="H7" s="3"/>
+      <c r="J7" s="5">
         <f>J6+1</f>
         <v>4</v>
       </c>
-      <c r="K7" s="15" t="s">
+      <c r="K7" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="L7" s="9" t="s">
+      <c r="L7" s="5" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="81" x14ac:dyDescent="0.25">
-      <c r="A8" s="7">
+    <row r="8" spans="1:12" ht="81.599999999999994" x14ac:dyDescent="0.25">
+      <c r="A8" s="3">
         <f>A7+1</f>
         <v>6</v>
       </c>
-      <c r="B8" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C8" s="7" t="s">
+      <c r="B8" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D8" s="10" t="s">
+      <c r="D8" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="E8" s="7" t="s">
+      <c r="E8" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F8" s="7" t="s">
+      <c r="F8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G8" s="7" t="s">
+      <c r="G8" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J8" s="9"/>
-      <c r="K8" s="9"/>
-      <c r="L8" s="9"/>
-    </row>
-    <row r="9" spans="1:12" ht="162" x14ac:dyDescent="0.25">
-      <c r="A9" s="7">
+      <c r="H8" s="3"/>
+      <c r="J8" s="5"/>
+      <c r="K8" s="5"/>
+      <c r="L8" s="5"/>
+    </row>
+    <row r="9" spans="1:12" ht="163.19999999999999" x14ac:dyDescent="0.25">
+      <c r="A9" s="3">
         <f>A8+1</f>
         <v>7</v>
       </c>
-      <c r="B9" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C9" s="7" t="s">
+      <c r="B9" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D9" s="10" t="s">
+      <c r="D9" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="E9" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="F9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G9" s="7" t="s">
+      <c r="G9" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J9" s="9"/>
-      <c r="K9" s="9"/>
-      <c r="L9" s="9"/>
-    </row>
-    <row r="10" spans="1:12" ht="162" x14ac:dyDescent="0.25">
-      <c r="A10" s="7">
+      <c r="H9" s="3"/>
+      <c r="J9" s="5"/>
+      <c r="K9" s="5"/>
+      <c r="L9" s="5"/>
+    </row>
+    <row r="10" spans="1:12" ht="163.19999999999999" x14ac:dyDescent="0.25">
+      <c r="A10" s="3">
         <f>A9+1</f>
         <v>8</v>
       </c>
-      <c r="B10" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C10" s="7" t="s">
+      <c r="B10" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D10" s="10" t="s">
+      <c r="D10" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="E10" s="7" t="s">
+      <c r="E10" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F10" s="7" t="s">
+      <c r="F10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G10" s="7" t="s">
+      <c r="G10" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J10" s="9"/>
-      <c r="K10" s="9"/>
-      <c r="L10" s="9"/>
-    </row>
-    <row r="11" spans="1:12" ht="182.25" x14ac:dyDescent="0.25">
-      <c r="A11" s="7"/>
-      <c r="B11" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C11" s="7" t="s">
+      <c r="H10" s="3"/>
+      <c r="J10" s="5"/>
+      <c r="K10" s="5"/>
+      <c r="L10" s="5"/>
+    </row>
+    <row r="11" spans="1:12" ht="183.6" x14ac:dyDescent="0.25">
+      <c r="A11" s="3"/>
+      <c r="B11" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D11" s="10" t="s">
+      <c r="D11" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="E11" s="7" t="s">
+      <c r="E11" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F11" s="7" t="s">
+      <c r="F11" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G11" s="7" t="s">
+      <c r="G11" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J11" s="9"/>
-      <c r="K11" s="9"/>
-      <c r="L11" s="9"/>
-    </row>
-    <row r="12" spans="1:12" ht="162" x14ac:dyDescent="0.25">
-      <c r="A12" s="7"/>
-      <c r="B12" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C12" s="7" t="s">
+      <c r="H11" s="3"/>
+      <c r="J11" s="5"/>
+      <c r="K11" s="5"/>
+      <c r="L11" s="5"/>
+    </row>
+    <row r="12" spans="1:12" ht="122.4" x14ac:dyDescent="0.25">
+      <c r="A12" s="3"/>
+      <c r="B12" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D12" s="10" t="s">
+      <c r="D12" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="E12" s="7" t="s">
+      <c r="E12" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F12" s="7" t="s">
+      <c r="F12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G12" s="7" t="s">
+      <c r="G12" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J12" s="9"/>
-      <c r="K12" s="9"/>
-      <c r="L12" s="9"/>
-    </row>
-    <row r="13" spans="1:12" ht="405" x14ac:dyDescent="0.25">
-      <c r="A13" s="7">
+      <c r="H12" s="3"/>
+      <c r="J12" s="5"/>
+      <c r="K12" s="5"/>
+      <c r="L12" s="5"/>
+    </row>
+    <row r="13" spans="1:12" ht="387.6" x14ac:dyDescent="0.25">
+      <c r="A13" s="3">
         <f>A10+1</f>
         <v>9</v>
       </c>
-      <c r="B13" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C13" s="7" t="s">
+      <c r="B13" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D13" s="10" t="s">
+      <c r="D13" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E13" s="7" t="s">
+      <c r="E13" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F13" s="7" t="s">
+      <c r="F13" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G13" s="7" t="s">
+      <c r="G13" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J13" s="9">
+      <c r="H13" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="J13" s="5">
         <f>J7+1</f>
         <v>5</v>
       </c>
-      <c r="K13" s="9"/>
-      <c r="L13" s="9"/>
-    </row>
-    <row r="14" spans="1:12" ht="81" x14ac:dyDescent="0.25">
-      <c r="A14" s="7">
+      <c r="K13" s="5"/>
+      <c r="L13" s="5"/>
+    </row>
+    <row r="14" spans="1:12" ht="61.2" x14ac:dyDescent="0.25">
+      <c r="A14" s="3">
         <f>A13+1</f>
         <v>10</v>
       </c>
-      <c r="B14" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C14" s="7" t="s">
+      <c r="B14" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D14" s="11" t="s">
+      <c r="D14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E14" s="11" t="s">
+      <c r="E14" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F14" s="7" t="s">
+      <c r="F14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G14" s="7" t="s">
+      <c r="G14" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J14" s="9">
+      <c r="H14" s="3"/>
+      <c r="J14" s="5">
         <f>J13+1</f>
         <v>6</v>
       </c>
-      <c r="K14" s="9"/>
-      <c r="L14" s="9"/>
-    </row>
-    <row r="15" spans="1:12" ht="182.25" x14ac:dyDescent="0.25">
-      <c r="A15" s="7">
+      <c r="K14" s="5"/>
+      <c r="L14" s="5"/>
+    </row>
+    <row r="15" spans="1:12" ht="184.8" x14ac:dyDescent="0.25">
+      <c r="A15" s="3">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="B15" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C15" s="7" t="s">
+      <c r="B15" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D15" s="7" t="s">
+      <c r="D15" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="E15" s="11" t="s">
+      <c r="E15" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F15" s="7" t="s">
+      <c r="F15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G15" s="7" t="s">
+      <c r="G15" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J15" s="9">
+      <c r="H15" s="3"/>
+      <c r="J15" s="5">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="K15" s="9"/>
-      <c r="L15" s="9"/>
-    </row>
-    <row r="16" spans="1:12" ht="81" x14ac:dyDescent="0.25">
-      <c r="A16" s="7">
+      <c r="K15" s="5"/>
+      <c r="L15" s="5"/>
+    </row>
+    <row r="16" spans="1:12" ht="61.2" x14ac:dyDescent="0.25">
+      <c r="A16" s="3">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="B16" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C16" s="7" t="s">
+      <c r="B16" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D16" s="7" t="s">
+      <c r="D16" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="E16" s="11" t="s">
+      <c r="E16" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F16" s="7" t="s">
+      <c r="F16" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G16" s="7" t="s">
+      <c r="G16" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J16" s="9">
+      <c r="H16" s="3"/>
+      <c r="J16" s="5">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="K16" s="9"/>
-      <c r="L16" s="9"/>
+      <c r="K16" s="5"/>
+      <c r="L16" s="5"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17" s="7">
+      <c r="A17" s="3">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="B17" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
-      <c r="G17" s="7"/>
-      <c r="J17" s="9">
+      <c r="B17" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C17" s="3"/>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="3"/>
+      <c r="H17" s="3"/>
+      <c r="J17" s="5">
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
-      <c r="K17" s="9"/>
-      <c r="L17" s="9"/>
+      <c r="K17" s="5"/>
+      <c r="L17" s="5"/>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18" s="7">
+      <c r="A18" s="3">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="B18" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="7"/>
-      <c r="G18" s="7"/>
-      <c r="J18" s="9">
+      <c r="B18" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C18" s="3"/>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="3"/>
+      <c r="H18" s="3"/>
+      <c r="J18" s="5">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="K18" s="9"/>
-      <c r="L18" s="9"/>
+      <c r="K18" s="5"/>
+      <c r="L18" s="5"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A19" s="7">
+      <c r="A19" s="3">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="B19" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="7"/>
-      <c r="G19" s="7"/>
-      <c r="J19" s="9">
+      <c r="B19" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C19" s="3"/>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3"/>
+      <c r="H19" s="3"/>
+      <c r="J19" s="5">
         <f t="shared" si="1"/>
         <v>11</v>
       </c>
-      <c r="K19" s="9"/>
-      <c r="L19" s="9"/>
+      <c r="K19" s="5"/>
+      <c r="L19" s="5"/>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A20" s="7">
+      <c r="A20" s="3">
         <f t="shared" ref="A20:A55" si="2">A19+1</f>
         <v>16</v>
       </c>
-      <c r="B20" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="7"/>
-      <c r="G20" s="7"/>
-      <c r="J20" s="9">
+      <c r="B20" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C20" s="3"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="3"/>
+      <c r="H20" s="3"/>
+      <c r="J20" s="5">
         <f t="shared" ref="J20:J55" si="3">J19+1</f>
         <v>12</v>
       </c>
-      <c r="K20" s="9"/>
-      <c r="L20" s="9"/>
+      <c r="K20" s="5"/>
+      <c r="L20" s="5"/>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A21" s="7">
+      <c r="A21" s="3">
         <f t="shared" si="2"/>
         <v>17</v>
       </c>
-      <c r="B21" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="7"/>
-      <c r="G21" s="7"/>
-      <c r="J21" s="9">
-        <f t="shared" si="3"/>
-        <v>13</v>
-      </c>
-      <c r="K21" s="9"/>
-      <c r="L21" s="9"/>
+      <c r="B21" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C21" s="3"/>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="3"/>
+      <c r="H21" s="3"/>
+      <c r="J21" s="5">
+        <f t="shared" si="3"/>
+        <v>13</v>
+      </c>
+      <c r="K21" s="5"/>
+      <c r="L21" s="5"/>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A22" s="7">
+      <c r="A22" s="3">
         <f t="shared" si="2"/>
         <v>18</v>
       </c>
-      <c r="B22" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="7"/>
-      <c r="G22" s="7"/>
-      <c r="J22" s="9">
+      <c r="B22" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C22" s="3"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3"/>
+      <c r="H22" s="3"/>
+      <c r="J22" s="5">
         <f t="shared" si="3"/>
         <v>14</v>
       </c>
-      <c r="K22" s="9"/>
-      <c r="L22" s="9"/>
+      <c r="K22" s="5"/>
+      <c r="L22" s="5"/>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A23" s="7">
+      <c r="A23" s="3">
         <f t="shared" si="2"/>
         <v>19</v>
       </c>
-      <c r="B23" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C23" s="7"/>
-      <c r="D23" s="7"/>
-      <c r="E23" s="7"/>
-      <c r="F23" s="7"/>
-      <c r="G23" s="7"/>
-      <c r="J23" s="9">
+      <c r="B23" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C23" s="3"/>
+      <c r="D23" s="3"/>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="3"/>
+      <c r="H23" s="3"/>
+      <c r="J23" s="5">
         <f t="shared" si="3"/>
         <v>15</v>
       </c>
-      <c r="K23" s="9"/>
-      <c r="L23" s="9"/>
+      <c r="K23" s="5"/>
+      <c r="L23" s="5"/>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A24" s="7">
+      <c r="A24" s="3">
         <f t="shared" si="2"/>
         <v>20</v>
       </c>
-      <c r="B24" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="7"/>
-      <c r="F24" s="7"/>
-      <c r="G24" s="7"/>
-      <c r="J24" s="9">
+      <c r="B24" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C24" s="3"/>
+      <c r="D24" s="3"/>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="3"/>
+      <c r="H24" s="3"/>
+      <c r="J24" s="5">
         <f t="shared" si="3"/>
         <v>16</v>
       </c>
-      <c r="K24" s="9"/>
-      <c r="L24" s="9"/>
+      <c r="K24" s="5"/>
+      <c r="L24" s="5"/>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A25" s="7">
+      <c r="A25" s="3">
         <f t="shared" si="2"/>
         <v>21</v>
       </c>
-      <c r="B25" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C25" s="7"/>
-      <c r="D25" s="7"/>
-      <c r="E25" s="7"/>
-      <c r="F25" s="7"/>
-      <c r="G25" s="7"/>
-      <c r="J25" s="9">
+      <c r="B25" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C25" s="3"/>
+      <c r="D25" s="3"/>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="3"/>
+      <c r="H25" s="3"/>
+      <c r="J25" s="5">
         <f t="shared" si="3"/>
         <v>17</v>
       </c>
-      <c r="K25" s="9"/>
-      <c r="L25" s="9"/>
+      <c r="K25" s="5"/>
+      <c r="L25" s="5"/>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A26" s="7">
+      <c r="A26" s="3">
         <f t="shared" si="2"/>
         <v>22</v>
       </c>
-      <c r="B26" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C26" s="7"/>
-      <c r="D26" s="7"/>
-      <c r="E26" s="7"/>
-      <c r="F26" s="7"/>
-      <c r="G26" s="7"/>
-      <c r="J26" s="9">
+      <c r="B26" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C26" s="3"/>
+      <c r="D26" s="3"/>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="3"/>
+      <c r="H26" s="3"/>
+      <c r="J26" s="5">
         <f t="shared" si="3"/>
         <v>18</v>
       </c>
-      <c r="K26" s="9"/>
-      <c r="L26" s="9"/>
+      <c r="K26" s="5"/>
+      <c r="L26" s="5"/>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A27" s="7">
+      <c r="A27" s="3">
         <f t="shared" si="2"/>
         <v>23</v>
       </c>
-      <c r="B27" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C27" s="7"/>
-      <c r="D27" s="7"/>
-      <c r="E27" s="7"/>
-      <c r="F27" s="7"/>
-      <c r="G27" s="7"/>
-      <c r="J27" s="9">
+      <c r="B27" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C27" s="3"/>
+      <c r="D27" s="3"/>
+      <c r="E27" s="3"/>
+      <c r="F27" s="3"/>
+      <c r="G27" s="3"/>
+      <c r="H27" s="3"/>
+      <c r="J27" s="5">
         <f t="shared" si="3"/>
         <v>19</v>
       </c>
-      <c r="K27" s="9"/>
-      <c r="L27" s="9"/>
+      <c r="K27" s="5"/>
+      <c r="L27" s="5"/>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A28" s="7">
+      <c r="A28" s="3">
         <f t="shared" si="2"/>
         <v>24</v>
       </c>
-      <c r="B28" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C28" s="7"/>
-      <c r="D28" s="7"/>
-      <c r="E28" s="7"/>
-      <c r="F28" s="7"/>
-      <c r="G28" s="7"/>
-      <c r="J28" s="9">
+      <c r="B28" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C28" s="3"/>
+      <c r="D28" s="3"/>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="3"/>
+      <c r="H28" s="3"/>
+      <c r="J28" s="5">
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
-      <c r="K28" s="9"/>
-      <c r="L28" s="9"/>
+      <c r="K28" s="5"/>
+      <c r="L28" s="5"/>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A29" s="7">
+      <c r="A29" s="3">
         <f t="shared" si="2"/>
         <v>25</v>
       </c>
-      <c r="B29" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C29" s="7"/>
-      <c r="D29" s="7"/>
-      <c r="E29" s="7"/>
-      <c r="F29" s="7"/>
-      <c r="G29" s="7"/>
-      <c r="J29" s="9">
+      <c r="B29" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C29" s="3"/>
+      <c r="D29" s="3"/>
+      <c r="E29" s="3"/>
+      <c r="F29" s="3"/>
+      <c r="G29" s="3"/>
+      <c r="H29" s="3"/>
+      <c r="J29" s="5">
         <f t="shared" si="3"/>
         <v>21</v>
       </c>
-      <c r="K29" s="9"/>
-      <c r="L29" s="9"/>
+      <c r="K29" s="5"/>
+      <c r="L29" s="5"/>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A30" s="7">
+      <c r="A30" s="3">
         <f t="shared" si="2"/>
         <v>26</v>
       </c>
-      <c r="B30" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C30" s="7"/>
-      <c r="D30" s="7"/>
-      <c r="E30" s="7"/>
-      <c r="F30" s="7"/>
-      <c r="G30" s="7"/>
-      <c r="J30" s="9">
+      <c r="B30" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C30" s="3"/>
+      <c r="D30" s="3"/>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="3"/>
+      <c r="H30" s="3"/>
+      <c r="J30" s="5">
         <f t="shared" si="3"/>
         <v>22</v>
       </c>
-      <c r="K30" s="9"/>
-      <c r="L30" s="9"/>
+      <c r="K30" s="5"/>
+      <c r="L30" s="5"/>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A31" s="7">
+      <c r="A31" s="3">
         <f t="shared" si="2"/>
         <v>27</v>
       </c>
-      <c r="B31" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C31" s="7"/>
-      <c r="D31" s="7"/>
-      <c r="E31" s="7"/>
-      <c r="F31" s="7"/>
-      <c r="G31" s="7"/>
-      <c r="J31" s="9">
+      <c r="B31" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C31" s="3"/>
+      <c r="D31" s="3"/>
+      <c r="E31" s="3"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="3"/>
+      <c r="H31" s="3"/>
+      <c r="J31" s="5">
         <f t="shared" si="3"/>
         <v>23</v>
       </c>
-      <c r="K31" s="9"/>
-      <c r="L31" s="9"/>
+      <c r="K31" s="5"/>
+      <c r="L31" s="5"/>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A32" s="7">
+      <c r="A32" s="3">
         <f t="shared" si="2"/>
         <v>28</v>
       </c>
-      <c r="B32" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C32" s="7"/>
-      <c r="D32" s="7"/>
-      <c r="E32" s="7"/>
-      <c r="F32" s="7"/>
-      <c r="G32" s="7"/>
-      <c r="J32" s="9">
+      <c r="B32" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C32" s="3"/>
+      <c r="D32" s="3"/>
+      <c r="E32" s="3"/>
+      <c r="F32" s="3"/>
+      <c r="G32" s="3"/>
+      <c r="H32" s="3"/>
+      <c r="J32" s="5">
         <f t="shared" si="3"/>
         <v>24</v>
       </c>
-      <c r="K32" s="9"/>
-      <c r="L32" s="9"/>
+      <c r="K32" s="5"/>
+      <c r="L32" s="5"/>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A33" s="7">
+      <c r="A33" s="3">
         <f t="shared" si="2"/>
         <v>29</v>
       </c>
-      <c r="B33" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C33" s="7"/>
-      <c r="D33" s="7"/>
-      <c r="E33" s="7"/>
-      <c r="F33" s="7"/>
-      <c r="G33" s="7"/>
-      <c r="J33" s="9">
+      <c r="B33" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C33" s="3"/>
+      <c r="D33" s="3"/>
+      <c r="E33" s="3"/>
+      <c r="F33" s="3"/>
+      <c r="G33" s="3"/>
+      <c r="H33" s="3"/>
+      <c r="J33" s="5">
         <f t="shared" si="3"/>
         <v>25</v>
       </c>
-      <c r="K33" s="9"/>
-      <c r="L33" s="9"/>
+      <c r="K33" s="5"/>
+      <c r="L33" s="5"/>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A34" s="7">
+      <c r="A34" s="3">
         <f t="shared" si="2"/>
         <v>30</v>
       </c>
-      <c r="B34" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C34" s="7"/>
-      <c r="D34" s="7"/>
-      <c r="E34" s="7"/>
-      <c r="F34" s="7"/>
-      <c r="G34" s="7"/>
-      <c r="J34" s="9">
+      <c r="B34" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C34" s="3"/>
+      <c r="D34" s="3"/>
+      <c r="E34" s="3"/>
+      <c r="F34" s="3"/>
+      <c r="G34" s="3"/>
+      <c r="H34" s="3"/>
+      <c r="J34" s="5">
         <f t="shared" si="3"/>
         <v>26</v>
       </c>
-      <c r="K34" s="9"/>
-      <c r="L34" s="9"/>
+      <c r="K34" s="5"/>
+      <c r="L34" s="5"/>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A35" s="7">
+      <c r="A35" s="3">
         <f t="shared" si="2"/>
         <v>31</v>
       </c>
-      <c r="B35" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C35" s="7"/>
-      <c r="D35" s="7"/>
-      <c r="E35" s="7"/>
-      <c r="F35" s="7"/>
-      <c r="G35" s="7"/>
-      <c r="J35" s="9">
+      <c r="B35" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C35" s="3"/>
+      <c r="D35" s="3"/>
+      <c r="E35" s="3"/>
+      <c r="F35" s="3"/>
+      <c r="G35" s="3"/>
+      <c r="H35" s="3"/>
+      <c r="J35" s="5">
         <f t="shared" si="3"/>
         <v>27</v>
       </c>
-      <c r="K35" s="9"/>
-      <c r="L35" s="9"/>
+      <c r="K35" s="5"/>
+      <c r="L35" s="5"/>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A36" s="7">
+      <c r="A36" s="3">
         <f t="shared" si="2"/>
         <v>32</v>
       </c>
-      <c r="B36" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C36" s="7"/>
-      <c r="D36" s="7"/>
-      <c r="E36" s="7"/>
-      <c r="F36" s="7"/>
-      <c r="G36" s="7"/>
-      <c r="J36" s="9">
+      <c r="B36" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C36" s="3"/>
+      <c r="D36" s="3"/>
+      <c r="E36" s="3"/>
+      <c r="F36" s="3"/>
+      <c r="G36" s="3"/>
+      <c r="H36" s="3"/>
+      <c r="J36" s="5">
         <f t="shared" si="3"/>
         <v>28</v>
       </c>
-      <c r="K36" s="9"/>
-      <c r="L36" s="9"/>
+      <c r="K36" s="5"/>
+      <c r="L36" s="5"/>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A37" s="7">
+      <c r="A37" s="3">
         <f t="shared" si="2"/>
         <v>33</v>
       </c>
-      <c r="B37" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C37" s="7"/>
-      <c r="D37" s="7"/>
-      <c r="E37" s="7"/>
-      <c r="F37" s="7"/>
-      <c r="G37" s="7"/>
-      <c r="J37" s="9">
+      <c r="B37" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C37" s="3"/>
+      <c r="D37" s="3"/>
+      <c r="E37" s="3"/>
+      <c r="F37" s="3"/>
+      <c r="G37" s="3"/>
+      <c r="H37" s="3"/>
+      <c r="J37" s="5">
         <f t="shared" si="3"/>
         <v>29</v>
       </c>
-      <c r="K37" s="9"/>
-      <c r="L37" s="9"/>
+      <c r="K37" s="5"/>
+      <c r="L37" s="5"/>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A38" s="7">
+      <c r="A38" s="3">
         <f t="shared" si="2"/>
         <v>34</v>
       </c>
-      <c r="B38" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C38" s="7"/>
-      <c r="D38" s="7"/>
-      <c r="E38" s="7"/>
-      <c r="F38" s="7"/>
-      <c r="G38" s="7"/>
-      <c r="J38" s="9">
+      <c r="B38" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C38" s="3"/>
+      <c r="D38" s="3"/>
+      <c r="E38" s="3"/>
+      <c r="F38" s="3"/>
+      <c r="G38" s="3"/>
+      <c r="H38" s="3"/>
+      <c r="J38" s="5">
         <f t="shared" si="3"/>
         <v>30</v>
       </c>
-      <c r="K38" s="9"/>
-      <c r="L38" s="9"/>
+      <c r="K38" s="5"/>
+      <c r="L38" s="5"/>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A39" s="7">
+      <c r="A39" s="3">
         <f t="shared" si="2"/>
         <v>35</v>
       </c>
-      <c r="B39" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C39" s="7"/>
-      <c r="D39" s="7"/>
-      <c r="E39" s="7"/>
-      <c r="F39" s="7"/>
-      <c r="G39" s="7"/>
-      <c r="J39" s="9">
+      <c r="B39" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C39" s="3"/>
+      <c r="D39" s="3"/>
+      <c r="E39" s="3"/>
+      <c r="F39" s="3"/>
+      <c r="G39" s="3"/>
+      <c r="H39" s="3"/>
+      <c r="J39" s="5">
         <f t="shared" si="3"/>
         <v>31</v>
       </c>
-      <c r="K39" s="9"/>
-      <c r="L39" s="9"/>
+      <c r="K39" s="5"/>
+      <c r="L39" s="5"/>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A40" s="7">
+      <c r="A40" s="3">
         <f t="shared" si="2"/>
         <v>36</v>
       </c>
-      <c r="B40" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C40" s="7"/>
-      <c r="D40" s="7"/>
-      <c r="E40" s="7"/>
-      <c r="F40" s="7"/>
-      <c r="G40" s="7"/>
-      <c r="J40" s="9">
+      <c r="B40" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C40" s="3"/>
+      <c r="D40" s="3"/>
+      <c r="E40" s="3"/>
+      <c r="F40" s="3"/>
+      <c r="G40" s="3"/>
+      <c r="H40" s="3"/>
+      <c r="J40" s="5">
         <f t="shared" si="3"/>
         <v>32</v>
       </c>
-      <c r="K40" s="9"/>
-      <c r="L40" s="9"/>
+      <c r="K40" s="5"/>
+      <c r="L40" s="5"/>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A41" s="7">
+      <c r="A41" s="3">
         <f t="shared" si="2"/>
         <v>37</v>
       </c>
-      <c r="B41" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C41" s="7"/>
-      <c r="D41" s="7"/>
-      <c r="E41" s="7"/>
-      <c r="F41" s="7"/>
-      <c r="G41" s="7"/>
-      <c r="J41" s="9">
+      <c r="B41" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C41" s="3"/>
+      <c r="D41" s="3"/>
+      <c r="E41" s="3"/>
+      <c r="F41" s="3"/>
+      <c r="G41" s="3"/>
+      <c r="H41" s="3"/>
+      <c r="J41" s="5">
         <f t="shared" si="3"/>
         <v>33</v>
       </c>
-      <c r="K41" s="9"/>
-      <c r="L41" s="9"/>
+      <c r="K41" s="5"/>
+      <c r="L41" s="5"/>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A42" s="7">
+      <c r="A42" s="3">
         <f t="shared" si="2"/>
         <v>38</v>
       </c>
-      <c r="B42" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C42" s="7"/>
-      <c r="D42" s="7"/>
-      <c r="E42" s="7"/>
-      <c r="F42" s="7"/>
-      <c r="G42" s="7"/>
-      <c r="J42" s="9">
+      <c r="B42" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C42" s="3"/>
+      <c r="D42" s="3"/>
+      <c r="E42" s="3"/>
+      <c r="F42" s="3"/>
+      <c r="G42" s="3"/>
+      <c r="H42" s="3"/>
+      <c r="J42" s="5">
         <f t="shared" si="3"/>
         <v>34</v>
       </c>
-      <c r="K42" s="9"/>
-      <c r="L42" s="9"/>
+      <c r="K42" s="5"/>
+      <c r="L42" s="5"/>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A43" s="7">
+      <c r="A43" s="3">
         <f t="shared" si="2"/>
         <v>39</v>
       </c>
-      <c r="B43" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C43" s="7"/>
-      <c r="D43" s="7"/>
-      <c r="E43" s="7"/>
-      <c r="F43" s="7"/>
-      <c r="G43" s="7"/>
-      <c r="J43" s="9">
+      <c r="B43" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C43" s="3"/>
+      <c r="D43" s="3"/>
+      <c r="E43" s="3"/>
+      <c r="F43" s="3"/>
+      <c r="G43" s="3"/>
+      <c r="H43" s="3"/>
+      <c r="J43" s="5">
         <f t="shared" si="3"/>
         <v>35</v>
       </c>
-      <c r="K43" s="9"/>
-      <c r="L43" s="9"/>
+      <c r="K43" s="5"/>
+      <c r="L43" s="5"/>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A44" s="7">
+      <c r="A44" s="3">
         <f t="shared" si="2"/>
         <v>40</v>
       </c>
-      <c r="B44" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C44" s="7"/>
-      <c r="D44" s="7"/>
-      <c r="E44" s="7"/>
-      <c r="F44" s="7"/>
-      <c r="G44" s="7"/>
-      <c r="J44" s="9">
+      <c r="B44" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C44" s="3"/>
+      <c r="D44" s="3"/>
+      <c r="E44" s="3"/>
+      <c r="F44" s="3"/>
+      <c r="G44" s="3"/>
+      <c r="H44" s="3"/>
+      <c r="J44" s="5">
         <f t="shared" si="3"/>
         <v>36</v>
       </c>
-      <c r="K44" s="9"/>
-      <c r="L44" s="9"/>
+      <c r="K44" s="5"/>
+      <c r="L44" s="5"/>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A45" s="7">
+      <c r="A45" s="3">
         <f t="shared" si="2"/>
         <v>41</v>
       </c>
-      <c r="B45" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C45" s="7"/>
-      <c r="D45" s="7"/>
-      <c r="E45" s="7"/>
-      <c r="F45" s="7"/>
-      <c r="G45" s="7"/>
-      <c r="J45" s="9">
+      <c r="B45" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C45" s="3"/>
+      <c r="D45" s="3"/>
+      <c r="E45" s="3"/>
+      <c r="F45" s="3"/>
+      <c r="G45" s="3"/>
+      <c r="H45" s="3"/>
+      <c r="J45" s="5">
         <f t="shared" si="3"/>
         <v>37</v>
       </c>
-      <c r="K45" s="9"/>
-      <c r="L45" s="9"/>
+      <c r="K45" s="5"/>
+      <c r="L45" s="5"/>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A46" s="7">
+      <c r="A46" s="3">
         <f t="shared" si="2"/>
         <v>42</v>
       </c>
-      <c r="B46" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C46" s="7"/>
-      <c r="D46" s="7"/>
-      <c r="E46" s="7"/>
-      <c r="F46" s="7"/>
-      <c r="G46" s="7"/>
-      <c r="J46" s="9">
+      <c r="B46" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C46" s="3"/>
+      <c r="D46" s="3"/>
+      <c r="E46" s="3"/>
+      <c r="F46" s="3"/>
+      <c r="G46" s="3"/>
+      <c r="H46" s="3"/>
+      <c r="J46" s="5">
         <f t="shared" si="3"/>
         <v>38</v>
       </c>
-      <c r="K46" s="9"/>
-      <c r="L46" s="9"/>
+      <c r="K46" s="5"/>
+      <c r="L46" s="5"/>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A47" s="7">
+      <c r="A47" s="3">
         <f t="shared" si="2"/>
         <v>43</v>
       </c>
-      <c r="B47" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C47" s="7"/>
-      <c r="D47" s="7"/>
-      <c r="E47" s="7"/>
-      <c r="F47" s="7"/>
-      <c r="G47" s="7"/>
-      <c r="J47" s="9">
+      <c r="B47" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C47" s="3"/>
+      <c r="D47" s="3"/>
+      <c r="E47" s="3"/>
+      <c r="F47" s="3"/>
+      <c r="G47" s="3"/>
+      <c r="H47" s="3"/>
+      <c r="J47" s="5">
         <f t="shared" si="3"/>
         <v>39</v>
       </c>
-      <c r="K47" s="9"/>
-      <c r="L47" s="9"/>
+      <c r="K47" s="5"/>
+      <c r="L47" s="5"/>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A48" s="7">
+      <c r="A48" s="3">
         <f t="shared" si="2"/>
         <v>44</v>
       </c>
-      <c r="B48" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C48" s="7"/>
-      <c r="D48" s="7"/>
-      <c r="E48" s="7"/>
-      <c r="F48" s="7"/>
-      <c r="G48" s="7"/>
-      <c r="J48" s="9">
+      <c r="B48" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C48" s="3"/>
+      <c r="D48" s="3"/>
+      <c r="E48" s="3"/>
+      <c r="F48" s="3"/>
+      <c r="G48" s="3"/>
+      <c r="H48" s="3"/>
+      <c r="J48" s="5">
         <f t="shared" si="3"/>
         <v>40</v>
       </c>
-      <c r="K48" s="9"/>
-      <c r="L48" s="9"/>
+      <c r="K48" s="5"/>
+      <c r="L48" s="5"/>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A49" s="7">
+      <c r="A49" s="3">
         <f t="shared" si="2"/>
         <v>45</v>
       </c>
-      <c r="B49" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C49" s="7"/>
-      <c r="D49" s="7"/>
-      <c r="E49" s="7"/>
-      <c r="F49" s="7"/>
-      <c r="G49" s="7"/>
-      <c r="J49" s="9">
+      <c r="B49" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C49" s="3"/>
+      <c r="D49" s="3"/>
+      <c r="E49" s="3"/>
+      <c r="F49" s="3"/>
+      <c r="G49" s="3"/>
+      <c r="H49" s="3"/>
+      <c r="J49" s="5">
         <f t="shared" si="3"/>
         <v>41</v>
       </c>
-      <c r="K49" s="9"/>
-      <c r="L49" s="9"/>
+      <c r="K49" s="5"/>
+      <c r="L49" s="5"/>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A50" s="7">
+      <c r="A50" s="3">
         <f t="shared" si="2"/>
         <v>46</v>
       </c>
-      <c r="B50" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C50" s="7"/>
-      <c r="D50" s="7"/>
-      <c r="E50" s="7"/>
-      <c r="F50" s="7"/>
-      <c r="G50" s="7"/>
-      <c r="J50" s="9">
+      <c r="B50" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C50" s="3"/>
+      <c r="D50" s="3"/>
+      <c r="E50" s="3"/>
+      <c r="F50" s="3"/>
+      <c r="G50" s="3"/>
+      <c r="H50" s="3"/>
+      <c r="J50" s="5">
         <f t="shared" si="3"/>
         <v>42</v>
       </c>
-      <c r="K50" s="9"/>
-      <c r="L50" s="9"/>
+      <c r="K50" s="5"/>
+      <c r="L50" s="5"/>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A51" s="7">
+      <c r="A51" s="3">
         <f t="shared" si="2"/>
         <v>47</v>
       </c>
-      <c r="B51" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C51" s="7"/>
-      <c r="D51" s="7"/>
-      <c r="E51" s="7"/>
-      <c r="F51" s="7"/>
-      <c r="G51" s="7"/>
-      <c r="J51" s="9">
+      <c r="B51" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C51" s="3"/>
+      <c r="D51" s="3"/>
+      <c r="E51" s="3"/>
+      <c r="F51" s="3"/>
+      <c r="G51" s="3"/>
+      <c r="H51" s="3"/>
+      <c r="J51" s="5">
         <f t="shared" si="3"/>
         <v>43</v>
       </c>
-      <c r="K51" s="9"/>
-      <c r="L51" s="9"/>
+      <c r="K51" s="5"/>
+      <c r="L51" s="5"/>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A52" s="7">
+      <c r="A52" s="3">
         <f t="shared" si="2"/>
         <v>48</v>
       </c>
-      <c r="B52" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C52" s="7"/>
-      <c r="D52" s="7"/>
-      <c r="E52" s="7"/>
-      <c r="F52" s="7"/>
-      <c r="G52" s="7"/>
-      <c r="J52" s="9">
+      <c r="B52" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C52" s="3"/>
+      <c r="D52" s="3"/>
+      <c r="E52" s="3"/>
+      <c r="F52" s="3"/>
+      <c r="G52" s="3"/>
+      <c r="H52" s="3"/>
+      <c r="J52" s="5">
         <f t="shared" si="3"/>
         <v>44</v>
       </c>
-      <c r="K52" s="9"/>
-      <c r="L52" s="9"/>
+      <c r="K52" s="5"/>
+      <c r="L52" s="5"/>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A53" s="7">
+      <c r="A53" s="3">
         <f t="shared" si="2"/>
         <v>49</v>
       </c>
-      <c r="B53" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C53" s="7"/>
-      <c r="D53" s="7"/>
-      <c r="E53" s="7"/>
-      <c r="F53" s="7"/>
-      <c r="G53" s="7"/>
-      <c r="J53" s="9">
+      <c r="B53" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C53" s="3"/>
+      <c r="D53" s="3"/>
+      <c r="E53" s="3"/>
+      <c r="F53" s="3"/>
+      <c r="G53" s="3"/>
+      <c r="H53" s="3"/>
+      <c r="J53" s="5">
         <f t="shared" si="3"/>
         <v>45</v>
       </c>
-      <c r="K53" s="9"/>
-      <c r="L53" s="9"/>
+      <c r="K53" s="5"/>
+      <c r="L53" s="5"/>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A54" s="7">
+      <c r="A54" s="3">
         <f t="shared" si="2"/>
         <v>50</v>
       </c>
-      <c r="B54" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C54" s="7"/>
-      <c r="D54" s="7"/>
-      <c r="E54" s="7"/>
-      <c r="F54" s="7"/>
-      <c r="G54" s="7"/>
-      <c r="J54" s="9">
+      <c r="B54" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C54" s="3"/>
+      <c r="D54" s="3"/>
+      <c r="E54" s="3"/>
+      <c r="F54" s="3"/>
+      <c r="G54" s="3"/>
+      <c r="H54" s="3"/>
+      <c r="J54" s="5">
         <f t="shared" si="3"/>
         <v>46</v>
       </c>
-      <c r="K54" s="9"/>
-      <c r="L54" s="9"/>
+      <c r="K54" s="5"/>
+      <c r="L54" s="5"/>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A55" s="7">
+      <c r="A55" s="3">
         <f t="shared" si="2"/>
         <v>51</v>
       </c>
-      <c r="B55" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C55" s="7"/>
-      <c r="D55" s="7"/>
-      <c r="E55" s="7"/>
-      <c r="F55" s="7"/>
-      <c r="G55" s="7"/>
-      <c r="J55" s="9">
+      <c r="B55" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C55" s="3"/>
+      <c r="D55" s="3"/>
+      <c r="E55" s="3"/>
+      <c r="F55" s="3"/>
+      <c r="G55" s="3"/>
+      <c r="H55" s="3"/>
+      <c r="J55" s="5">
         <f t="shared" si="3"/>
         <v>47</v>
       </c>
-      <c r="K55" s="9"/>
-      <c r="L55" s="9"/>
+      <c r="K55" s="5"/>
+      <c r="L55" s="5"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="J2:L2"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
@@ -2693,6 +2755,7 @@
     <mergeCell ref="F1:F2"/>
     <mergeCell ref="G1:G2"/>
     <mergeCell ref="C1:C2"/>
+    <mergeCell ref="H1:H2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docs/spec/ARM.xlsx
+++ b/docs/spec/ARM.xlsx
@@ -5,15 +5,16 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\taoma\Downloads\ADSS_Group_Y\docs\spec\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\EitanKrimer\Documents\university\ADSS\ADSS_Group_Y\docs\spec\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C6ADC19-3E30-42F8-8A0A-C1D87F865897}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{377030A4-4488-43DB-BC9E-7FEEAD587ABD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-60" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="ARM" sheetId="1" r:id="rId1"/>
+    <sheet name="Unclear" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="37">
   <si>
     <t>ID</t>
   </si>
@@ -874,12 +875,6 @@
   </si>
   <si>
     <t>???</t>
-  </si>
-  <si>
-    <t>priority</t>
-  </si>
-  <si>
-    <t>First</t>
   </si>
 </sst>
 </file>
@@ -890,7 +885,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -909,7 +904,7 @@
     <font>
       <sz val="16"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -1437,23 +1432,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L55"/>
-  <sheetFormatPr defaultColWidth="9.09765625" defaultRowHeight="20.399999999999999" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:G55"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="21" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.09765625" style="2"/>
-    <col min="2" max="2" width="15.3984375" style="2" customWidth="1"/>
+    <col min="1" max="1" width="9.140625" style="2"/>
+    <col min="2" max="2" width="15.42578125" style="2" customWidth="1"/>
     <col min="3" max="3" width="10" style="2" customWidth="1"/>
-    <col min="4" max="4" width="43.59765625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="12.09765625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="9.09765625" style="2"/>
-    <col min="7" max="8" width="26.296875" style="2" customWidth="1"/>
-    <col min="9" max="10" width="9.09765625" style="2"/>
-    <col min="11" max="11" width="33.69921875" style="2" customWidth="1"/>
-    <col min="12" max="12" width="46.59765625" style="2" customWidth="1"/>
-    <col min="13" max="16384" width="9.09765625" style="2"/>
+    <col min="4" max="4" width="43.5703125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="12.140625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="9.140625" style="2"/>
+    <col min="7" max="7" width="26.28515625" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
@@ -1475,11 +1467,8 @@
       <c r="G1" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="11" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="12"/>
       <c r="B2" s="12"/>
       <c r="C2" s="14"/>
@@ -1487,14 +1476,8 @@
       <c r="E2" s="12"/>
       <c r="F2" s="12"/>
       <c r="G2" s="12"/>
-      <c r="H2" s="12"/>
-      <c r="J2" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="K2" s="9"/>
-      <c r="L2" s="10"/>
-    </row>
-    <row r="3" spans="1:12" ht="61.2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:7" ht="81" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>1</v>
       </c>
@@ -1504,8 +1487,8 @@
       <c r="C3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>17</v>
+      <c r="D3" s="6" t="s">
+        <v>21</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>6</v>
@@ -1516,18 +1499,8 @@
       <c r="G3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="H3" s="3"/>
-      <c r="J3" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" ht="135" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:7" ht="162" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <f>A3+1</f>
         <v>2</v>
@@ -1536,10 +1509,10 @@
         <v>13</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>20</v>
+        <v>14</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>6</v>
@@ -1550,33 +1523,23 @@
       <c r="G4" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="H4" s="3"/>
-      <c r="J4" s="1">
-        <v>1</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="L4" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" ht="122.4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:7" ht="141.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
-        <f>A4+1</f>
+        <f t="shared" ref="A5:A16" si="0">A4+1</f>
         <v>3</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>32</v>
+        <v>14</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>23</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>8</v>
@@ -1584,31 +1547,20 @@
       <c r="G5" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="H5" s="3"/>
-      <c r="J5" s="5">
-        <f>J4+1</f>
-        <v>2</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="L5" s="5" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" ht="142.80000000000001" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:7" ht="182.25" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
-        <f t="shared" ref="A6:A19" si="0">A5+1</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>18</v>
+        <v>14</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>6</v>
@@ -1619,31 +1571,20 @@
       <c r="G6" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="H6" s="3"/>
-      <c r="J6" s="5">
-        <f t="shared" ref="J6:J19" si="1">J5+1</f>
-        <v>3</v>
-      </c>
-      <c r="K6" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="L6" s="5" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" ht="142.80000000000001" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:7" ht="162" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
-        <f>A6+1</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>19</v>
+        <v>14</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>27</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>6</v>
@@ -1654,21 +1595,10 @@
       <c r="G7" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="H7" s="3"/>
-      <c r="J7" s="5">
-        <f>J6+1</f>
-        <v>4</v>
-      </c>
-      <c r="K7" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="L7" s="5" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" ht="81.599999999999994" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:7" ht="405" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
-        <f>A7+1</f>
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="B8" s="3" t="s">
@@ -1678,7 +1608,7 @@
         <v>14</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>6</v>
@@ -1689,14 +1619,10 @@
       <c r="G8" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="H8" s="3"/>
-      <c r="J8" s="5"/>
-      <c r="K8" s="5"/>
-      <c r="L8" s="5"/>
-    </row>
-    <row r="9" spans="1:12" ht="163.19999999999999" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:7" ht="60.75" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
-        <f>A8+1</f>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="B9" s="3" t="s">
@@ -1705,8 +1631,8 @@
       <c r="C9" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D9" s="6" t="s">
-        <v>22</v>
+      <c r="D9" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>6</v>
@@ -1717,14 +1643,10 @@
       <c r="G9" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="H9" s="3"/>
-      <c r="J9" s="5"/>
-      <c r="K9" s="5"/>
-      <c r="L9" s="5"/>
-    </row>
-    <row r="10" spans="1:12" ht="163.19999999999999" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:7" ht="101.25" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
-        <f>A9+1</f>
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="B10" s="3" t="s">
@@ -1733,8 +1655,8 @@
       <c r="C10" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D10" s="6" t="s">
-        <v>23</v>
+      <c r="D10" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>6</v>
@@ -1745,24 +1667,23 @@
       <c r="G10" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="H10" s="3"/>
-      <c r="J10" s="5"/>
-      <c r="K10" s="5"/>
-      <c r="L10" s="5"/>
-    </row>
-    <row r="11" spans="1:12" ht="183.6" x14ac:dyDescent="0.25">
-      <c r="A11" s="3"/>
+    </row>
+    <row r="11" spans="1:7" ht="121.5" x14ac:dyDescent="0.25">
+      <c r="A11" s="3">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
       <c r="B11" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>25</v>
+        <v>16</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>32</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F11" s="3" t="s">
         <v>8</v>
@@ -1770,21 +1691,20 @@
       <c r="G11" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="H11" s="3"/>
-      <c r="J11" s="5"/>
-      <c r="K11" s="5"/>
-      <c r="L11" s="5"/>
-    </row>
-    <row r="12" spans="1:12" ht="122.4" x14ac:dyDescent="0.25">
-      <c r="A12" s="3"/>
+    </row>
+    <row r="12" spans="1:7" ht="141.75" x14ac:dyDescent="0.25">
+      <c r="A12" s="3">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
       <c r="B12" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>27</v>
+        <v>16</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>18</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>6</v>
@@ -1795,24 +1715,20 @@
       <c r="G12" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="H12" s="3"/>
-      <c r="J12" s="5"/>
-      <c r="K12" s="5"/>
-      <c r="L12" s="5"/>
-    </row>
-    <row r="13" spans="1:12" ht="387.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="13" spans="1:7" ht="81" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
-        <f>A10+1</f>
-        <v>9</v>
+        <f t="shared" si="0"/>
+        <v>11</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>6</v>
@@ -1823,20 +1739,11 @@
       <c r="G13" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="H13" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="J13" s="5">
-        <f>J7+1</f>
-        <v>5</v>
-      </c>
-      <c r="K13" s="5"/>
-      <c r="L13" s="5"/>
-    </row>
-    <row r="14" spans="1:12" ht="61.2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="14" spans="1:7" ht="81" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
-        <f>A13+1</f>
-        <v>10</v>
+        <f t="shared" si="0"/>
+        <v>12</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>13</v>
@@ -1856,18 +1763,11 @@
       <c r="G14" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="H14" s="3"/>
-      <c r="J14" s="5">
-        <f>J13+1</f>
-        <v>6</v>
-      </c>
-      <c r="K14" s="5"/>
-      <c r="L14" s="5"/>
-    </row>
-    <row r="15" spans="1:12" ht="184.8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="15" spans="1:7" ht="182.25" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>13</v>
@@ -1887,18 +1787,11 @@
       <c r="G15" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="H15" s="3"/>
-      <c r="J15" s="5">
-        <f t="shared" si="1"/>
-        <v>7</v>
-      </c>
-      <c r="K15" s="5"/>
-      <c r="L15" s="5"/>
-    </row>
-    <row r="16" spans="1:12" ht="61.2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="16" spans="1:7" ht="81" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>13</v>
@@ -1918,18 +1811,11 @@
       <c r="G16" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="H16" s="3"/>
-      <c r="J16" s="5">
-        <f t="shared" si="1"/>
-        <v>8</v>
-      </c>
-      <c r="K16" s="5"/>
-      <c r="L16" s="5"/>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
-        <f t="shared" si="0"/>
-        <v>13</v>
+        <f t="shared" ref="A17:A19" si="1">A16+1</f>
+        <v>15</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>13</v>
@@ -1939,18 +1825,11 @@
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
-      <c r="H17" s="3"/>
-      <c r="J17" s="5">
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="3">
         <f t="shared" si="1"/>
-        <v>9</v>
-      </c>
-      <c r="K17" s="5"/>
-      <c r="L17" s="5"/>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18" s="3">
-        <f t="shared" si="0"/>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>13</v>
@@ -1960,18 +1839,11 @@
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
-      <c r="J18" s="5">
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="3">
         <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="K18" s="5"/>
-      <c r="L18" s="5"/>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A19" s="3">
-        <f t="shared" si="0"/>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>13</v>
@@ -1981,18 +1853,11 @@
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
       <c r="G19" s="3"/>
-      <c r="H19" s="3"/>
-      <c r="J19" s="5">
-        <f t="shared" si="1"/>
-        <v>11</v>
-      </c>
-      <c r="K19" s="5"/>
-      <c r="L19" s="5"/>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
         <f t="shared" ref="A20:A55" si="2">A19+1</f>
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>13</v>
@@ -2002,18 +1867,11 @@
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
       <c r="G20" s="3"/>
-      <c r="H20" s="3"/>
-      <c r="J20" s="5">
-        <f t="shared" ref="J20:J55" si="3">J19+1</f>
-        <v>12</v>
-      </c>
-      <c r="K20" s="5"/>
-      <c r="L20" s="5"/>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
         <f t="shared" si="2"/>
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>13</v>
@@ -2023,18 +1881,11 @@
       <c r="E21" s="3"/>
       <c r="F21" s="3"/>
       <c r="G21" s="3"/>
-      <c r="H21" s="3"/>
-      <c r="J21" s="5">
-        <f t="shared" si="3"/>
-        <v>13</v>
-      </c>
-      <c r="K21" s="5"/>
-      <c r="L21" s="5"/>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="3">
         <f t="shared" si="2"/>
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>13</v>
@@ -2044,18 +1895,11 @@
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
       <c r="G22" s="3"/>
-      <c r="H22" s="3"/>
-      <c r="J22" s="5">
-        <f t="shared" si="3"/>
-        <v>14</v>
-      </c>
-      <c r="K22" s="5"/>
-      <c r="L22" s="5"/>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="3">
         <f t="shared" si="2"/>
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>13</v>
@@ -2065,18 +1909,11 @@
       <c r="E23" s="3"/>
       <c r="F23" s="3"/>
       <c r="G23" s="3"/>
-      <c r="H23" s="3"/>
-      <c r="J23" s="5">
-        <f t="shared" si="3"/>
-        <v>15</v>
-      </c>
-      <c r="K23" s="5"/>
-      <c r="L23" s="5"/>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="3">
         <f t="shared" si="2"/>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>13</v>
@@ -2086,18 +1923,11 @@
       <c r="E24" s="3"/>
       <c r="F24" s="3"/>
       <c r="G24" s="3"/>
-      <c r="H24" s="3"/>
-      <c r="J24" s="5">
-        <f t="shared" si="3"/>
-        <v>16</v>
-      </c>
-      <c r="K24" s="5"/>
-      <c r="L24" s="5"/>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="3">
         <f t="shared" si="2"/>
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>13</v>
@@ -2107,18 +1937,11 @@
       <c r="E25" s="3"/>
       <c r="F25" s="3"/>
       <c r="G25" s="3"/>
-      <c r="H25" s="3"/>
-      <c r="J25" s="5">
-        <f t="shared" si="3"/>
-        <v>17</v>
-      </c>
-      <c r="K25" s="5"/>
-      <c r="L25" s="5"/>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="3">
         <f t="shared" si="2"/>
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>13</v>
@@ -2128,18 +1951,11 @@
       <c r="E26" s="3"/>
       <c r="F26" s="3"/>
       <c r="G26" s="3"/>
-      <c r="H26" s="3"/>
-      <c r="J26" s="5">
-        <f t="shared" si="3"/>
-        <v>18</v>
-      </c>
-      <c r="K26" s="5"/>
-      <c r="L26" s="5"/>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="3">
         <f t="shared" si="2"/>
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>13</v>
@@ -2149,18 +1965,11 @@
       <c r="E27" s="3"/>
       <c r="F27" s="3"/>
       <c r="G27" s="3"/>
-      <c r="H27" s="3"/>
-      <c r="J27" s="5">
-        <f t="shared" si="3"/>
-        <v>19</v>
-      </c>
-      <c r="K27" s="5"/>
-      <c r="L27" s="5"/>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="3">
         <f t="shared" si="2"/>
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>13</v>
@@ -2170,18 +1979,11 @@
       <c r="E28" s="3"/>
       <c r="F28" s="3"/>
       <c r="G28" s="3"/>
-      <c r="H28" s="3"/>
-      <c r="J28" s="5">
-        <f t="shared" si="3"/>
-        <v>20</v>
-      </c>
-      <c r="K28" s="5"/>
-      <c r="L28" s="5"/>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="3">
         <f t="shared" si="2"/>
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>13</v>
@@ -2191,18 +1993,11 @@
       <c r="E29" s="3"/>
       <c r="F29" s="3"/>
       <c r="G29" s="3"/>
-      <c r="H29" s="3"/>
-      <c r="J29" s="5">
-        <f t="shared" si="3"/>
-        <v>21</v>
-      </c>
-      <c r="K29" s="5"/>
-      <c r="L29" s="5"/>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="3">
         <f t="shared" si="2"/>
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>13</v>
@@ -2212,18 +2007,11 @@
       <c r="E30" s="3"/>
       <c r="F30" s="3"/>
       <c r="G30" s="3"/>
-      <c r="H30" s="3"/>
-      <c r="J30" s="5">
-        <f t="shared" si="3"/>
-        <v>22</v>
-      </c>
-      <c r="K30" s="5"/>
-      <c r="L30" s="5"/>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="3">
         <f t="shared" si="2"/>
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>13</v>
@@ -2233,18 +2021,11 @@
       <c r="E31" s="3"/>
       <c r="F31" s="3"/>
       <c r="G31" s="3"/>
-      <c r="H31" s="3"/>
-      <c r="J31" s="5">
-        <f t="shared" si="3"/>
-        <v>23</v>
-      </c>
-      <c r="K31" s="5"/>
-      <c r="L31" s="5"/>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="3">
         <f t="shared" si="2"/>
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>13</v>
@@ -2254,18 +2035,11 @@
       <c r="E32" s="3"/>
       <c r="F32" s="3"/>
       <c r="G32" s="3"/>
-      <c r="H32" s="3"/>
-      <c r="J32" s="5">
-        <f t="shared" si="3"/>
-        <v>24</v>
-      </c>
-      <c r="K32" s="5"/>
-      <c r="L32" s="5"/>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="3">
         <f t="shared" si="2"/>
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>13</v>
@@ -2275,18 +2049,11 @@
       <c r="E33" s="3"/>
       <c r="F33" s="3"/>
       <c r="G33" s="3"/>
-      <c r="H33" s="3"/>
-      <c r="J33" s="5">
-        <f t="shared" si="3"/>
-        <v>25</v>
-      </c>
-      <c r="K33" s="5"/>
-      <c r="L33" s="5"/>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="3">
         <f t="shared" si="2"/>
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>13</v>
@@ -2296,18 +2063,11 @@
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
       <c r="G34" s="3"/>
-      <c r="H34" s="3"/>
-      <c r="J34" s="5">
-        <f t="shared" si="3"/>
-        <v>26</v>
-      </c>
-      <c r="K34" s="5"/>
-      <c r="L34" s="5"/>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="3">
         <f t="shared" si="2"/>
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>13</v>
@@ -2317,18 +2077,11 @@
       <c r="E35" s="3"/>
       <c r="F35" s="3"/>
       <c r="G35" s="3"/>
-      <c r="H35" s="3"/>
-      <c r="J35" s="5">
-        <f t="shared" si="3"/>
-        <v>27</v>
-      </c>
-      <c r="K35" s="5"/>
-      <c r="L35" s="5"/>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="3">
         <f t="shared" si="2"/>
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>13</v>
@@ -2338,18 +2091,11 @@
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
       <c r="G36" s="3"/>
-      <c r="H36" s="3"/>
-      <c r="J36" s="5">
-        <f t="shared" si="3"/>
-        <v>28</v>
-      </c>
-      <c r="K36" s="5"/>
-      <c r="L36" s="5"/>
-    </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="3">
         <f t="shared" si="2"/>
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>13</v>
@@ -2359,18 +2105,11 @@
       <c r="E37" s="3"/>
       <c r="F37" s="3"/>
       <c r="G37" s="3"/>
-      <c r="H37" s="3"/>
-      <c r="J37" s="5">
-        <f t="shared" si="3"/>
-        <v>29</v>
-      </c>
-      <c r="K37" s="5"/>
-      <c r="L37" s="5"/>
-    </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="3">
         <f t="shared" si="2"/>
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>13</v>
@@ -2380,18 +2119,11 @@
       <c r="E38" s="3"/>
       <c r="F38" s="3"/>
       <c r="G38" s="3"/>
-      <c r="H38" s="3"/>
-      <c r="J38" s="5">
-        <f t="shared" si="3"/>
-        <v>30</v>
-      </c>
-      <c r="K38" s="5"/>
-      <c r="L38" s="5"/>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="3">
         <f t="shared" si="2"/>
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>13</v>
@@ -2401,18 +2133,11 @@
       <c r="E39" s="3"/>
       <c r="F39" s="3"/>
       <c r="G39" s="3"/>
-      <c r="H39" s="3"/>
-      <c r="J39" s="5">
-        <f t="shared" si="3"/>
-        <v>31</v>
-      </c>
-      <c r="K39" s="5"/>
-      <c r="L39" s="5"/>
-    </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="3">
         <f t="shared" si="2"/>
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>13</v>
@@ -2422,18 +2147,11 @@
       <c r="E40" s="3"/>
       <c r="F40" s="3"/>
       <c r="G40" s="3"/>
-      <c r="H40" s="3"/>
-      <c r="J40" s="5">
-        <f t="shared" si="3"/>
-        <v>32</v>
-      </c>
-      <c r="K40" s="5"/>
-      <c r="L40" s="5"/>
-    </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="3">
         <f t="shared" si="2"/>
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>13</v>
@@ -2443,18 +2161,11 @@
       <c r="E41" s="3"/>
       <c r="F41" s="3"/>
       <c r="G41" s="3"/>
-      <c r="H41" s="3"/>
-      <c r="J41" s="5">
-        <f t="shared" si="3"/>
-        <v>33</v>
-      </c>
-      <c r="K41" s="5"/>
-      <c r="L41" s="5"/>
-    </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="3">
         <f t="shared" si="2"/>
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B42" s="3" t="s">
         <v>13</v>
@@ -2464,18 +2175,11 @@
       <c r="E42" s="3"/>
       <c r="F42" s="3"/>
       <c r="G42" s="3"/>
-      <c r="H42" s="3"/>
-      <c r="J42" s="5">
-        <f t="shared" si="3"/>
-        <v>34</v>
-      </c>
-      <c r="K42" s="5"/>
-      <c r="L42" s="5"/>
-    </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="3">
         <f t="shared" si="2"/>
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B43" s="3" t="s">
         <v>13</v>
@@ -2485,18 +2189,11 @@
       <c r="E43" s="3"/>
       <c r="F43" s="3"/>
       <c r="G43" s="3"/>
-      <c r="H43" s="3"/>
-      <c r="J43" s="5">
-        <f t="shared" si="3"/>
-        <v>35</v>
-      </c>
-      <c r="K43" s="5"/>
-      <c r="L43" s="5"/>
-    </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="3">
         <f t="shared" si="2"/>
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>13</v>
@@ -2506,18 +2203,11 @@
       <c r="E44" s="3"/>
       <c r="F44" s="3"/>
       <c r="G44" s="3"/>
-      <c r="H44" s="3"/>
-      <c r="J44" s="5">
-        <f t="shared" si="3"/>
-        <v>36</v>
-      </c>
-      <c r="K44" s="5"/>
-      <c r="L44" s="5"/>
-    </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="3">
         <f t="shared" si="2"/>
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>13</v>
@@ -2527,18 +2217,11 @@
       <c r="E45" s="3"/>
       <c r="F45" s="3"/>
       <c r="G45" s="3"/>
-      <c r="H45" s="3"/>
-      <c r="J45" s="5">
-        <f t="shared" si="3"/>
-        <v>37</v>
-      </c>
-      <c r="K45" s="5"/>
-      <c r="L45" s="5"/>
-    </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="3">
         <f t="shared" si="2"/>
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>13</v>
@@ -2548,18 +2231,11 @@
       <c r="E46" s="3"/>
       <c r="F46" s="3"/>
       <c r="G46" s="3"/>
-      <c r="H46" s="3"/>
-      <c r="J46" s="5">
-        <f t="shared" si="3"/>
-        <v>38</v>
-      </c>
-      <c r="K46" s="5"/>
-      <c r="L46" s="5"/>
-    </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="3">
         <f t="shared" si="2"/>
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B47" s="3" t="s">
         <v>13</v>
@@ -2569,18 +2245,11 @@
       <c r="E47" s="3"/>
       <c r="F47" s="3"/>
       <c r="G47" s="3"/>
-      <c r="H47" s="3"/>
-      <c r="J47" s="5">
-        <f t="shared" si="3"/>
-        <v>39</v>
-      </c>
-      <c r="K47" s="5"/>
-      <c r="L47" s="5"/>
-    </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="3">
         <f t="shared" si="2"/>
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B48" s="3" t="s">
         <v>13</v>
@@ -2590,18 +2259,11 @@
       <c r="E48" s="3"/>
       <c r="F48" s="3"/>
       <c r="G48" s="3"/>
-      <c r="H48" s="3"/>
-      <c r="J48" s="5">
-        <f t="shared" si="3"/>
-        <v>40</v>
-      </c>
-      <c r="K48" s="5"/>
-      <c r="L48" s="5"/>
-    </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="3">
         <f t="shared" si="2"/>
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B49" s="3" t="s">
         <v>13</v>
@@ -2611,18 +2273,11 @@
       <c r="E49" s="3"/>
       <c r="F49" s="3"/>
       <c r="G49" s="3"/>
-      <c r="H49" s="3"/>
-      <c r="J49" s="5">
-        <f t="shared" si="3"/>
-        <v>41</v>
-      </c>
-      <c r="K49" s="5"/>
-      <c r="L49" s="5"/>
-    </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="3">
         <f t="shared" si="2"/>
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B50" s="3" t="s">
         <v>13</v>
@@ -2632,18 +2287,11 @@
       <c r="E50" s="3"/>
       <c r="F50" s="3"/>
       <c r="G50" s="3"/>
-      <c r="H50" s="3"/>
-      <c r="J50" s="5">
-        <f t="shared" si="3"/>
-        <v>42</v>
-      </c>
-      <c r="K50" s="5"/>
-      <c r="L50" s="5"/>
-    </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="3">
         <f t="shared" si="2"/>
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B51" s="3" t="s">
         <v>13</v>
@@ -2653,18 +2301,11 @@
       <c r="E51" s="3"/>
       <c r="F51" s="3"/>
       <c r="G51" s="3"/>
-      <c r="H51" s="3"/>
-      <c r="J51" s="5">
-        <f t="shared" si="3"/>
-        <v>43</v>
-      </c>
-      <c r="K51" s="5"/>
-      <c r="L51" s="5"/>
-    </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="3">
         <f t="shared" si="2"/>
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B52" s="3" t="s">
         <v>13</v>
@@ -2674,18 +2315,11 @@
       <c r="E52" s="3"/>
       <c r="F52" s="3"/>
       <c r="G52" s="3"/>
-      <c r="H52" s="3"/>
-      <c r="J52" s="5">
-        <f t="shared" si="3"/>
-        <v>44</v>
-      </c>
-      <c r="K52" s="5"/>
-      <c r="L52" s="5"/>
-    </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="3">
         <f t="shared" si="2"/>
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B53" s="3" t="s">
         <v>13</v>
@@ -2695,18 +2329,11 @@
       <c r="E53" s="3"/>
       <c r="F53" s="3"/>
       <c r="G53" s="3"/>
-      <c r="H53" s="3"/>
-      <c r="J53" s="5">
-        <f t="shared" si="3"/>
-        <v>45</v>
-      </c>
-      <c r="K53" s="5"/>
-      <c r="L53" s="5"/>
-    </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="3">
         <f t="shared" si="2"/>
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B54" s="3" t="s">
         <v>13</v>
@@ -2716,18 +2343,11 @@
       <c r="E54" s="3"/>
       <c r="F54" s="3"/>
       <c r="G54" s="3"/>
-      <c r="H54" s="3"/>
-      <c r="J54" s="5">
-        <f t="shared" si="3"/>
-        <v>46</v>
-      </c>
-      <c r="K54" s="5"/>
-      <c r="L54" s="5"/>
-    </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="3">
         <f t="shared" si="2"/>
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B55" s="3" t="s">
         <v>13</v>
@@ -2737,17 +2357,9 @@
       <c r="E55" s="3"/>
       <c r="F55" s="3"/>
       <c r="G55" s="3"/>
-      <c r="H55" s="3"/>
-      <c r="J55" s="5">
-        <f t="shared" si="3"/>
-        <v>47</v>
-      </c>
-      <c r="K55" s="5"/>
-      <c r="L55" s="5"/>
     </row>
   </sheetData>
-  <mergeCells count="9">
-    <mergeCell ref="J2:L2"/>
+  <mergeCells count="7">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="D1:D2"/>
@@ -2755,7 +2367,113 @@
     <mergeCell ref="F1:F2"/>
     <mergeCell ref="G1:G2"/>
     <mergeCell ref="C1:C2"/>
-    <mergeCell ref="H1:H2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6A548FC-132A-4BCF-B26C-A9E84109E40A}">
+  <dimension ref="A1:C11"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="30" customWidth="1"/>
+    <col min="3" max="3" width="34.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="21" x14ac:dyDescent="0.25">
+      <c r="A1" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="10"/>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>1</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A4" s="5">
+        <f>A3+1</f>
+        <v>2</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="405" x14ac:dyDescent="0.25">
+      <c r="A5" s="5">
+        <f>A4+1</f>
+        <v>3</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A6" s="5">
+        <f>A5+1</f>
+        <v>4</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="21" x14ac:dyDescent="0.25">
+      <c r="A7" s="5"/>
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
+    </row>
+    <row r="8" spans="1:3" ht="21" x14ac:dyDescent="0.25">
+      <c r="A8" s="5"/>
+      <c r="B8" s="5"/>
+      <c r="C8" s="5"/>
+    </row>
+    <row r="9" spans="1:3" ht="21" x14ac:dyDescent="0.25">
+      <c r="A9" s="5"/>
+      <c r="B9" s="5"/>
+      <c r="C9" s="5"/>
+    </row>
+    <row r="10" spans="1:3" ht="21" x14ac:dyDescent="0.25">
+      <c r="A10" s="5"/>
+      <c r="B10" s="5"/>
+      <c r="C10" s="5"/>
+    </row>
+    <row r="11" spans="1:3" ht="21" x14ac:dyDescent="0.25">
+      <c r="A11" s="5"/>
+      <c r="B11" s="5"/>
+      <c r="C11" s="5"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docs/spec/ARM.xlsx
+++ b/docs/spec/ARM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\EitanKrimer\Documents\university\ADSS\ADSS_Group_Y\docs\spec\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{377030A4-4488-43DB-BC9E-7FEEAD587ABD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4E98275-9B86-4231-8B76-9911F0432A3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ARM" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="39">
   <si>
     <t>ID</t>
   </si>
@@ -390,31 +390,6 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve"> the supplies should be distribued.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">The System must follow this format for </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FFFF66FF"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Delivery File</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>:
-- Item ID (FK to actual item)
-- amount</t>
     </r>
   </si>
   <si>
@@ -524,6 +499,434 @@
     <r>
       <rPr>
         <sz val="16"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Transport Issue Log</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>:
+- Current Truck ID
+- New Truck ID
+- Unloaded items at Site ID
+- Unloaded Items Delivery File ID</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Upon maximum truck weight overflow - the system will ask the </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>TransportManager</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> which strategy to use:
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="16"/>
+        <color rgb="FFE90505"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>cancel or change one of the destinations</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+- change truck
+- unload certain items from the current truck</t>
+    </r>
+  </si>
+  <si>
+    <t>Upon maximum truck weight overflow - the system will ask the TransportManager which strategy to use:
+- cancel or change one of the destinations
+- change truck
+- unload certain items from the current truck</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Don’t know what to do when
+"cancel or change one of the destinations" </t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="9" tint="-0.249977111117893"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>System</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> can not allow a </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="7" tint="-0.499984740745262"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>driver</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> without a sufficent drivers license type to drive any </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>truck</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">A </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Transport Manager</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> in The </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="9" tint="-0.249977111117893"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>System</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> can define a variaty of </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>transport areas</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> - allowing the system to organize the </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Trucks</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> of the different Transports.</t>
+    </r>
+  </si>
+  <si>
+    <t>NTH or MH?</t>
+  </si>
+  <si>
+    <t>How to alert?</t>
+  </si>
+  <si>
+    <t>בנוגע ל "אחראי ההובלה"
+מי הוא אחראי ההובלה מבחינתך?
+האם מדובר במשתמש מערכת שמחליט ברגע יצירת הובלה את ההתנהלות המועדפת בעת חריגה?</t>
+  </si>
+  <si>
+    <t>???</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The System must follow this format for </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="16"/>
+        <color rgb="FF002060"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Delivery File Item</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>:
+- ID
+- Item ID(FK)
+- amount</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The System must follow this format for </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FFFF66FF"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Delivery File</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">:
+- ID
+- list of </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="16"/>
+        <color rgb="FF002060"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Delivery File Item</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>(s) IDs(FKs)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The System must follow this format for </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FFA50021"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Branch</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>:
+- ID
+- Branch name
+- Branch address
+- Branch phone</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">For any Transport in the System, a Transport should have:
+- Transport ID
+- planned datetime of transport
+- status (pending, started, done, done with issues)
+- Truck ID (FK to link to the </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFE90505"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>actual truck</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">)
+- Driver ID (FK to link to the actual </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="7" tint="-0.499984740745262"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>driver</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">)
+- source - List of </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="5" tint="0.39997558519241921"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Site</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">(s) ID(s) (FKs)
+- destination - List of </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="5" tint="0.39997558519241921"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Site</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">(s) ID(s) (FKs)
+- List of </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Transport Issue Log</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> ID(s) (FK)
+- actual start datetime
+- actual end datetime</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The System must follow this format for </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
         <color theme="5" tint="0.39997558519241921"/>
         <rFont val="Arial"/>
         <family val="2"/>
@@ -543,345 +946,16 @@
 - site object FK
 - contact phone
 - contact name
-- OPTIONAL Delivery File ID ( FK to actual Delivery File)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">For any Transport in the System, a Transport should have:
-- Transport ID
-- planned datetime of transport
-- status (pending, started, done, done with issues)
-- Truck ID (FK to link to the </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FFE90505"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>actual truck</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">)
-- Driver ID (FK to link to the actual </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color theme="7" tint="-0.499984740745262"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>driver</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">)
-- source - List of </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color theme="5" tint="0.39997558519241921"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Site</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">(s) ID(s) (FKs)
-- destination - List of </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color theme="5" tint="0.39997558519241921"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Site</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">(s) ID(s) (FKs)
-- List of </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Transport Issue Log</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> ID(s) (FK)
-- actual start datetime
-- initial truck weight</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">The System must follow this format for </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Transport Issue Log</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>:
-- Current Truck ID
-- New Truck ID
-- Unloaded items at Site ID
-- Unloaded Items Delivery File ID</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Upon maximum truck weight overflow - the system will ask the </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF7030A0"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>TransportManager</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> which strategy to use:
-- </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="16"/>
-        <color rgb="FFE90505"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>cancel or change one of the destinations</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-- change truck
-- unload certain items from the current truck</t>
-    </r>
-  </si>
-  <si>
-    <t>Upon maximum truck weight overflow - the system will ask the TransportManager which strategy to use:
-- cancel or change one of the destinations
-- change truck
-- unload certain items from the current truck</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Don’t know what to do when
-"cancel or change one of the destinations" </t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">The </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color theme="9" tint="-0.249977111117893"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>System</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> can not allow a </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color theme="7" tint="-0.499984740745262"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>driver</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> without a sufficent drivers license type to drive any </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>truck</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">A </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF7030A0"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Transport Manager</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> in The </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color theme="9" tint="-0.249977111117893"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>System</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> can define a variaty of </t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="16"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>transport areas</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> - allowing the system to organize the </t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="16"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Trucks</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> of the different Transports.</t>
-    </r>
-  </si>
-  <si>
-    <t>NTH or MH?</t>
-  </si>
-  <si>
-    <t>How to alert?</t>
-  </si>
-  <si>
-    <t>בנוגע ל "אחראי ההובלה"
-מי הוא אחראי ההובלה מבחינתך?
-האם מדובר במשתמש מערכת שמחליט ברגע יצירת הובלה את ההתנהלות המועדפת בעת חריגה?</t>
-  </si>
-  <si>
-    <t>???</t>
+- OPTIONAL Delivery File ID ( FK to actual Delivery File)
+- OPTIONAL Recroded weight at site</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="25" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1001,6 +1075,43 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FF002060"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FFE90505"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="7" tint="-0.499984740745262"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="5" tint="0.39997558519241921"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF00B0F0"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1100,7 +1211,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
@@ -1123,14 +1234,8 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
@@ -1144,6 +1249,18 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1152,9 +1269,9 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFA50021"/>
       <color rgb="FFE90505"/>
       <color rgb="FFFF66FF"/>
-      <color rgb="FFA50021"/>
       <color rgb="FF336699"/>
     </mruColors>
   </colors>
@@ -1432,7 +1549,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G55"/>
+  <dimension ref="A1:G57"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="21" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="2"/>
@@ -1446,38 +1563,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="D1" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="E1" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="F1" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="11" t="s">
+      <c r="G1" s="9" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="12"/>
-      <c r="B2" s="12"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="12"/>
-      <c r="E2" s="12"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="12"/>
-    </row>
-    <row r="3" spans="1:7" ht="81" x14ac:dyDescent="0.25">
+      <c r="A2" s="10"/>
+      <c r="B2" s="10"/>
+      <c r="C2" s="12"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+    </row>
+    <row r="3" spans="1:7" ht="101.25" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>1</v>
       </c>
@@ -1488,19 +1605,15 @@
         <v>14</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>8</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="E3" s="8"/>
+      <c r="F3" s="8"/>
       <c r="G3" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="162" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="101.25" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <f>A3+1</f>
         <v>2</v>
@@ -1512,7 +1625,7 @@
         <v>14</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>6</v>
@@ -1524,9 +1637,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="141.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="162" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
-        <f t="shared" ref="A5:A16" si="0">A4+1</f>
+        <f>A4+1</f>
         <v>3</v>
       </c>
       <c r="B5" s="3" t="s">
@@ -1536,7 +1649,7 @@
         <v>14</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>6</v>
@@ -1548,9 +1661,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="182.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="141.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="A6:A18" si="0">A5+1</f>
         <v>4</v>
       </c>
       <c r="B6" s="3" t="s">
@@ -1560,7 +1673,7 @@
         <v>14</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>6</v>
@@ -1572,7 +1685,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="162" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="141.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -1584,7 +1697,7 @@
         <v>14</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>6</v>
@@ -1596,7 +1709,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="405" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="222.75" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -1608,7 +1721,7 @@
         <v>14</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>6</v>
@@ -1620,7 +1733,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="60.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="140.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -1631,8 +1744,8 @@
       <c r="C9" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>17</v>
+      <c r="D9" s="6" t="s">
+        <v>24</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>6</v>
@@ -1644,7 +1757,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="101.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="342" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -1655,8 +1768,8 @@
       <c r="C10" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D10" s="4" t="s">
-        <v>20</v>
+      <c r="D10" s="16" t="s">
+        <v>37</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>6</v>
@@ -1668,7 +1781,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="121.5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="60.75" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -1677,13 +1790,13 @@
         <v>13</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F11" s="3" t="s">
         <v>8</v>
@@ -1692,7 +1805,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="141.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="101.25" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -1701,10 +1814,10 @@
         <v>13</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>6</v>
@@ -1716,7 +1829,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="81" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="101.25" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -1728,10 +1841,10 @@
         <v>16</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F13" s="3" t="s">
         <v>8</v>
@@ -1740,7 +1853,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="81" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="141.75" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -1751,8 +1864,8 @@
       <c r="C14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>24</v>
+      <c r="D14" s="4" t="s">
+        <v>18</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>6</v>
@@ -1764,7 +1877,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="182.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="81" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -1776,7 +1889,7 @@
         <v>16</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>6</v>
@@ -1800,7 +1913,7 @@
         <v>16</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>6</v>
@@ -1812,37 +1925,57 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="182.25" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
-        <f t="shared" ref="A17:A19" si="1">A16+1</f>
+        <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C17" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="81" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
+      <c r="C18" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="A19:A21" si="1">A18+1</f>
         <v>17</v>
       </c>
       <c r="B19" s="3" t="s">
@@ -1856,7 +1989,7 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
-        <f t="shared" ref="A20:A55" si="2">A19+1</f>
+        <f t="shared" si="1"/>
         <v>18</v>
       </c>
       <c r="B20" s="3" t="s">
@@ -1870,7 +2003,7 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>19</v>
       </c>
       <c r="B21" s="3" t="s">
@@ -1884,7 +2017,7 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="A22:A57" si="2">A21+1</f>
         <v>20</v>
       </c>
       <c r="B22" s="3" t="s">
@@ -2358,15 +2491,43 @@
       <c r="F55" s="3"/>
       <c r="G55" s="3"/>
     </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A56" s="3">
+        <f t="shared" si="2"/>
+        <v>54</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C56" s="3"/>
+      <c r="D56" s="3"/>
+      <c r="E56" s="3"/>
+      <c r="F56" s="3"/>
+      <c r="G56" s="3"/>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A57" s="3">
+        <f t="shared" si="2"/>
+        <v>55</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C57" s="3"/>
+      <c r="D57" s="3"/>
+      <c r="E57" s="3"/>
+      <c r="F57" s="3"/>
+      <c r="G57" s="3"/>
+    </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="C1:C2"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="D1:D2"/>
     <mergeCell ref="E1:E2"/>
     <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="C1:C2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2382,11 +2543,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="21" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="10"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="15"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -2399,51 +2560,51 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="135" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="409.5" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="162" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
         <f>A3+1</f>
         <v>2</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="405" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="101.25" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <f>A4+1</f>
         <v>3</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="409.5" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="168" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
         <f>A5+1</f>
         <v>4</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="21" x14ac:dyDescent="0.25">

--- a/docs/spec/ARM.xlsx
+++ b/docs/spec/ARM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\EitanKrimer\Documents\university\ADSS\ADSS_Group_Y\docs\spec\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4E98275-9B86-4231-8B76-9911F0432A3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBB33EFA-9F31-449B-B084-A44D2B0EBB48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ARM" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="52">
   <si>
     <t>ID</t>
   </si>
@@ -950,12 +950,662 @@
 - OPTIONAL Recroded weight at site</t>
     </r>
   </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>System</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> must allow a </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>transport manager</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> to start a </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="5" tint="-0.249977111117893"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>transport</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="9" tint="-0.249977111117893"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>System</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> must allow a </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>transport manager</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> to create a future </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="5" tint="-0.249977111117893"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>transport</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>System</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> must allow a </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>transport manager</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> to update a </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="5" tint="-0.249977111117893"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>transport</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>System</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> must allow a </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>transport manager</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> to delete a </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="5" tint="-0.249977111117893"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>transport</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>System</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> must allow a </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>transport manager</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> a transport manager to create a </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="7" tint="-0.249977111117893"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>driver</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>System</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> must allow a </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>transport manager</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> to edit a </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="7" tint="-0.249977111117893"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>driver</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>System</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> must allow a </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>transport manager</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> to delete a </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="7" tint="-0.249977111117893"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>driver</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>System</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> must allow a </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>transport manager</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> to create a </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>truck</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>System</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> must allow a </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>transport manager</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> to edit a </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>truck</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>System</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> must allow a </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>transport manager</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> to delete a </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>truck</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>System</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> must allow a </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>admin</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> to create a </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>branch</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>System</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> must allow a </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>admin</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> to edit a </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>branch</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>System</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> must allow a </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>admin</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> to delete a </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>branch</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="25" x14ac:knownFonts="1">
+  <fonts count="28" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1112,13 +1762,43 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="16"/>
+      <color rgb="FF00B050"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="7" tint="-0.249977111117893"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color rgb="FFC00000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="7">
@@ -1211,7 +1891,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
@@ -1220,9 +1900,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1236,6 +1913,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
@@ -1258,8 +1938,11 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1549,7 +2232,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G57"/>
+  <dimension ref="A1:G70"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="21" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="2"/>
@@ -1604,11 +2287,11 @@
       <c r="C3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
       <c r="G3" s="3" t="s">
         <v>15</v>
       </c>
@@ -1624,7 +2307,7 @@
       <c r="C4" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="5" t="s">
         <v>35</v>
       </c>
       <c r="E4" s="3" t="s">
@@ -1648,7 +2331,7 @@
       <c r="C5" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="5" t="s">
         <v>21</v>
       </c>
       <c r="E5" s="3" t="s">
@@ -1663,7 +2346,7 @@
     </row>
     <row r="6" spans="1:7" ht="141.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
-        <f t="shared" ref="A6:A18" si="0">A5+1</f>
+        <f t="shared" ref="A6:A31" si="0">A5+1</f>
         <v>4</v>
       </c>
       <c r="B6" s="3" t="s">
@@ -1672,7 +2355,7 @@
       <c r="C6" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="5" t="s">
         <v>22</v>
       </c>
       <c r="E6" s="3" t="s">
@@ -1696,7 +2379,7 @@
       <c r="C7" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="5" t="s">
         <v>36</v>
       </c>
       <c r="E7" s="3" t="s">
@@ -1720,7 +2403,7 @@
       <c r="C8" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D8" s="5" t="s">
         <v>38</v>
       </c>
       <c r="E8" s="3" t="s">
@@ -1744,7 +2427,7 @@
       <c r="C9" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="5" t="s">
         <v>24</v>
       </c>
       <c r="E9" s="3" t="s">
@@ -1768,7 +2451,7 @@
       <c r="C10" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D10" s="16" t="s">
+      <c r="D10" s="8" t="s">
         <v>37</v>
       </c>
       <c r="E10" s="3" t="s">
@@ -1816,7 +2499,7 @@
       <c r="C12" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="3" t="s">
         <v>20</v>
       </c>
       <c r="E12" s="3" t="s">
@@ -1829,32 +2512,32 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="101.25" x14ac:dyDescent="0.25">
-      <c r="A13" s="3">
+    <row r="13" spans="1:7" ht="121.5" x14ac:dyDescent="0.25">
+      <c r="A13" s="16">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C13" s="3" t="s">
+      <c r="B13" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="C13" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="D13" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="E13" s="3" t="s">
+      <c r="E13" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="F13" s="3" t="s">
+      <c r="F13" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="G13" s="3" t="s">
+      <c r="G13" s="16" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="141.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="3">
+    <row r="14" spans="1:7" ht="60.75" x14ac:dyDescent="0.25">
+      <c r="A14" s="17">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
@@ -1864,8 +2547,8 @@
       <c r="C14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D14" s="4" t="s">
-        <v>18</v>
+      <c r="D14" s="17" t="s">
+        <v>40</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>6</v>
@@ -1877,8 +2560,8 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="81" x14ac:dyDescent="0.25">
-      <c r="A15" s="3">
+    <row r="15" spans="1:7" ht="60.75" x14ac:dyDescent="0.25">
+      <c r="A15" s="17">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
@@ -1888,8 +2571,8 @@
       <c r="C15" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>19</v>
+      <c r="D15" s="17" t="s">
+        <v>39</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>6</v>
@@ -1901,8 +2584,8 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="81" x14ac:dyDescent="0.25">
-      <c r="A16" s="3">
+    <row r="16" spans="1:7" ht="60.75" x14ac:dyDescent="0.25">
+      <c r="A16" s="17">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
@@ -1912,8 +2595,8 @@
       <c r="C16" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D16" s="3" t="s">
-        <v>23</v>
+      <c r="D16" s="17" t="s">
+        <v>41</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>6</v>
@@ -1925,8 +2608,8 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="182.25" x14ac:dyDescent="0.25">
-      <c r="A17" s="3">
+    <row r="17" spans="1:7" ht="60.75" x14ac:dyDescent="0.25">
+      <c r="A17" s="17">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
@@ -1936,8 +2619,8 @@
       <c r="C17" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>25</v>
+      <c r="D17" s="17" t="s">
+        <v>42</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>6</v>
@@ -1949,8 +2632,8 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="81" x14ac:dyDescent="0.25">
-      <c r="A18" s="3">
+    <row r="18" spans="1:7" ht="60.75" x14ac:dyDescent="0.25">
+      <c r="A18" s="17">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
@@ -1960,8 +2643,8 @@
       <c r="C18" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>28</v>
+      <c r="D18" s="17" t="s">
+        <v>43</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>6</v>
@@ -1973,192 +2656,322 @@
         <v>15</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="3">
-        <f t="shared" ref="A19:A21" si="1">A18+1</f>
+    <row r="19" spans="1:7" ht="60.75" x14ac:dyDescent="0.25">
+      <c r="A19" s="17">
+        <f t="shared" si="0"/>
         <v>17</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="3">
-        <f t="shared" si="1"/>
+      <c r="C19" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D19" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="60.75" x14ac:dyDescent="0.25">
+      <c r="A20" s="17">
+        <f t="shared" si="0"/>
         <v>18</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C20" s="3"/>
-      <c r="D20" s="3"/>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3"/>
-      <c r="G20" s="3"/>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="3">
-        <f t="shared" si="1"/>
+      <c r="C20" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D20" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="60.75" x14ac:dyDescent="0.25">
+      <c r="A21" s="17">
+        <f t="shared" si="0"/>
         <v>19</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C21" s="3"/>
-      <c r="D21" s="3"/>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
-      <c r="G21" s="3"/>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="3">
-        <f t="shared" ref="A22:A57" si="2">A21+1</f>
+      <c r="C21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D21" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="60.75" x14ac:dyDescent="0.25">
+      <c r="A22" s="17">
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C22" s="3"/>
-      <c r="D22" s="3"/>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
-      <c r="G22" s="3"/>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="3">
-        <f t="shared" si="2"/>
+      <c r="C22" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D22" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="60.75" x14ac:dyDescent="0.25">
+      <c r="A23" s="17">
+        <f t="shared" si="0"/>
         <v>21</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C23" s="3"/>
-      <c r="D23" s="3"/>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
-      <c r="G23" s="3"/>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="3">
-        <f t="shared" si="2"/>
+      <c r="C23" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D23" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="40.5" x14ac:dyDescent="0.25">
+      <c r="A24" s="17">
+        <f t="shared" si="0"/>
         <v>22</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C24" s="3"/>
-      <c r="D24" s="3"/>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
-      <c r="G24" s="3"/>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="3">
-        <f t="shared" si="2"/>
+      <c r="C24" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D24" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="40.5" x14ac:dyDescent="0.25">
+      <c r="A25" s="17">
+        <f t="shared" si="0"/>
         <v>23</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C25" s="3"/>
-      <c r="D25" s="3"/>
-      <c r="E25" s="3"/>
-      <c r="F25" s="3"/>
-      <c r="G25" s="3"/>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="3">
-        <f t="shared" si="2"/>
+      <c r="C25" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D25" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="40.5" x14ac:dyDescent="0.25">
+      <c r="A26" s="17">
+        <f t="shared" si="0"/>
         <v>24</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C26" s="3"/>
-      <c r="D26" s="3"/>
-      <c r="E26" s="3"/>
-      <c r="F26" s="3"/>
-      <c r="G26" s="3"/>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="3">
-        <f t="shared" si="2"/>
+      <c r="C26" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D26" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="141.75" x14ac:dyDescent="0.25">
+      <c r="A27" s="17">
+        <f>A23+1</f>
+        <v>22</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="81" x14ac:dyDescent="0.25">
+      <c r="A28" s="3">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="81" x14ac:dyDescent="0.25">
+      <c r="A29" s="3">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="182.25" x14ac:dyDescent="0.25">
+      <c r="A30" s="3">
+        <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="B27" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C27" s="3"/>
-      <c r="D27" s="3"/>
-      <c r="E27" s="3"/>
-      <c r="F27" s="3"/>
-      <c r="G27" s="3"/>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="3">
-        <f t="shared" si="2"/>
+      <c r="B30" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="81" x14ac:dyDescent="0.25">
+      <c r="A31" s="3">
+        <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="B28" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C28" s="3"/>
-      <c r="D28" s="3"/>
-      <c r="E28" s="3"/>
-      <c r="F28" s="3"/>
-      <c r="G28" s="3"/>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="3">
-        <f t="shared" si="2"/>
-        <v>27</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C29" s="3"/>
-      <c r="D29" s="3"/>
-      <c r="E29" s="3"/>
-      <c r="F29" s="3"/>
-      <c r="G29" s="3"/>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="3">
-        <f t="shared" si="2"/>
+      <c r="B31" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D31" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B30" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C30" s="3"/>
-      <c r="D30" s="3"/>
-      <c r="E30" s="3"/>
-      <c r="F30" s="3"/>
-      <c r="G30" s="3"/>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="3">
-        <f t="shared" si="2"/>
-        <v>29</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C31" s="3"/>
-      <c r="D31" s="3"/>
-      <c r="E31" s="3"/>
-      <c r="F31" s="3"/>
-      <c r="G31" s="3"/>
+      <c r="E31" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="3">
-        <f t="shared" si="2"/>
-        <v>30</v>
+        <f t="shared" ref="A32:A34" si="1">A31+1</f>
+        <v>27</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>13</v>
@@ -2171,8 +2984,8 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="3">
-        <f t="shared" si="2"/>
-        <v>31</v>
+        <f t="shared" si="1"/>
+        <v>28</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>13</v>
@@ -2185,8 +2998,8 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="3">
-        <f t="shared" si="2"/>
-        <v>32</v>
+        <f t="shared" si="1"/>
+        <v>29</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>13</v>
@@ -2199,8 +3012,8 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="3">
-        <f t="shared" si="2"/>
-        <v>33</v>
+        <f t="shared" ref="A35:A70" si="2">A34+1</f>
+        <v>30</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>13</v>
@@ -2214,7 +3027,7 @@
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="3">
         <f t="shared" si="2"/>
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>13</v>
@@ -2228,7 +3041,7 @@
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="3">
         <f t="shared" si="2"/>
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>13</v>
@@ -2242,7 +3055,7 @@
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="3">
         <f t="shared" si="2"/>
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>13</v>
@@ -2256,7 +3069,7 @@
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="3">
         <f t="shared" si="2"/>
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>13</v>
@@ -2270,7 +3083,7 @@
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="3">
         <f t="shared" si="2"/>
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>13</v>
@@ -2284,7 +3097,7 @@
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="3">
         <f t="shared" si="2"/>
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>13</v>
@@ -2298,7 +3111,7 @@
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="3">
         <f t="shared" si="2"/>
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B42" s="3" t="s">
         <v>13</v>
@@ -2312,7 +3125,7 @@
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="3">
         <f t="shared" si="2"/>
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B43" s="3" t="s">
         <v>13</v>
@@ -2326,7 +3139,7 @@
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="3">
         <f t="shared" si="2"/>
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>13</v>
@@ -2340,7 +3153,7 @@
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="3">
         <f t="shared" si="2"/>
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>13</v>
@@ -2354,7 +3167,7 @@
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="3">
         <f t="shared" si="2"/>
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>13</v>
@@ -2368,7 +3181,7 @@
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="3">
         <f t="shared" si="2"/>
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B47" s="3" t="s">
         <v>13</v>
@@ -2382,7 +3195,7 @@
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="3">
         <f t="shared" si="2"/>
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B48" s="3" t="s">
         <v>13</v>
@@ -2396,7 +3209,7 @@
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="3">
         <f t="shared" si="2"/>
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B49" s="3" t="s">
         <v>13</v>
@@ -2410,7 +3223,7 @@
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="3">
         <f t="shared" si="2"/>
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B50" s="3" t="s">
         <v>13</v>
@@ -2424,7 +3237,7 @@
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="3">
         <f t="shared" si="2"/>
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B51" s="3" t="s">
         <v>13</v>
@@ -2438,7 +3251,7 @@
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="3">
         <f t="shared" si="2"/>
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B52" s="3" t="s">
         <v>13</v>
@@ -2452,7 +3265,7 @@
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="3">
         <f t="shared" si="2"/>
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B53" s="3" t="s">
         <v>13</v>
@@ -2466,7 +3279,7 @@
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="3">
         <f t="shared" si="2"/>
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B54" s="3" t="s">
         <v>13</v>
@@ -2480,7 +3293,7 @@
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="3">
         <f t="shared" si="2"/>
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B55" s="3" t="s">
         <v>13</v>
@@ -2494,7 +3307,7 @@
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="3">
         <f t="shared" si="2"/>
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B56" s="3" t="s">
         <v>13</v>
@@ -2508,7 +3321,7 @@
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="3">
         <f t="shared" si="2"/>
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B57" s="3" t="s">
         <v>13</v>
@@ -2518,6 +3331,188 @@
       <c r="E57" s="3"/>
       <c r="F57" s="3"/>
       <c r="G57" s="3"/>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A58" s="3">
+        <f t="shared" si="2"/>
+        <v>53</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C58" s="3"/>
+      <c r="D58" s="3"/>
+      <c r="E58" s="3"/>
+      <c r="F58" s="3"/>
+      <c r="G58" s="3"/>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A59" s="3">
+        <f t="shared" si="2"/>
+        <v>54</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C59" s="3"/>
+      <c r="D59" s="3"/>
+      <c r="E59" s="3"/>
+      <c r="F59" s="3"/>
+      <c r="G59" s="3"/>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A60" s="3">
+        <f t="shared" si="2"/>
+        <v>55</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C60" s="3"/>
+      <c r="D60" s="3"/>
+      <c r="E60" s="3"/>
+      <c r="F60" s="3"/>
+      <c r="G60" s="3"/>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A61" s="3">
+        <f t="shared" si="2"/>
+        <v>56</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C61" s="3"/>
+      <c r="D61" s="3"/>
+      <c r="E61" s="3"/>
+      <c r="F61" s="3"/>
+      <c r="G61" s="3"/>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A62" s="3">
+        <f t="shared" si="2"/>
+        <v>57</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C62" s="3"/>
+      <c r="D62" s="3"/>
+      <c r="E62" s="3"/>
+      <c r="F62" s="3"/>
+      <c r="G62" s="3"/>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A63" s="3">
+        <f t="shared" si="2"/>
+        <v>58</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C63" s="3"/>
+      <c r="D63" s="3"/>
+      <c r="E63" s="3"/>
+      <c r="F63" s="3"/>
+      <c r="G63" s="3"/>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A64" s="3">
+        <f t="shared" si="2"/>
+        <v>59</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C64" s="3"/>
+      <c r="D64" s="3"/>
+      <c r="E64" s="3"/>
+      <c r="F64" s="3"/>
+      <c r="G64" s="3"/>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A65" s="3">
+        <f t="shared" si="2"/>
+        <v>60</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C65" s="3"/>
+      <c r="D65" s="3"/>
+      <c r="E65" s="3"/>
+      <c r="F65" s="3"/>
+      <c r="G65" s="3"/>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A66" s="3">
+        <f t="shared" si="2"/>
+        <v>61</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C66" s="3"/>
+      <c r="D66" s="3"/>
+      <c r="E66" s="3"/>
+      <c r="F66" s="3"/>
+      <c r="G66" s="3"/>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A67" s="3">
+        <f t="shared" si="2"/>
+        <v>62</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C67" s="3"/>
+      <c r="D67" s="3"/>
+      <c r="E67" s="3"/>
+      <c r="F67" s="3"/>
+      <c r="G67" s="3"/>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A68" s="3">
+        <f t="shared" si="2"/>
+        <v>63</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C68" s="3"/>
+      <c r="D68" s="3"/>
+      <c r="E68" s="3"/>
+      <c r="F68" s="3"/>
+      <c r="G68" s="3"/>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A69" s="3">
+        <f t="shared" si="2"/>
+        <v>64</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C69" s="3"/>
+      <c r="D69" s="3"/>
+      <c r="E69" s="3"/>
+      <c r="F69" s="3"/>
+      <c r="G69" s="3"/>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A70" s="3">
+        <f t="shared" si="2"/>
+        <v>65</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C70" s="3"/>
+      <c r="D70" s="3"/>
+      <c r="E70" s="3"/>
+      <c r="F70" s="3"/>
+      <c r="G70" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -2572,65 +3567,65 @@
       </c>
     </row>
     <row r="4" spans="1:3" ht="162" x14ac:dyDescent="0.25">
-      <c r="A4" s="5">
+      <c r="A4" s="4">
         <f>A3+1</f>
         <v>2</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="4" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="101.25" x14ac:dyDescent="0.25">
-      <c r="A5" s="5">
+      <c r="A5" s="4">
         <f>A4+1</f>
         <v>3</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="4" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="168" x14ac:dyDescent="0.25">
-      <c r="A6" s="5">
+      <c r="A6" s="4">
         <f>A5+1</f>
         <v>4</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="4" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="21" x14ac:dyDescent="0.25">
-      <c r="A7" s="5"/>
-      <c r="B7" s="5"/>
-      <c r="C7" s="5"/>
+      <c r="A7" s="4"/>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
     </row>
     <row r="8" spans="1:3" ht="21" x14ac:dyDescent="0.25">
-      <c r="A8" s="5"/>
-      <c r="B8" s="5"/>
-      <c r="C8" s="5"/>
+      <c r="A8" s="4"/>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
     </row>
     <row r="9" spans="1:3" ht="21" x14ac:dyDescent="0.25">
-      <c r="A9" s="5"/>
-      <c r="B9" s="5"/>
-      <c r="C9" s="5"/>
+      <c r="A9" s="4"/>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
     </row>
     <row r="10" spans="1:3" ht="21" x14ac:dyDescent="0.25">
-      <c r="A10" s="5"/>
-      <c r="B10" s="5"/>
-      <c r="C10" s="5"/>
+      <c r="A10" s="4"/>
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
     </row>
     <row r="11" spans="1:3" ht="21" x14ac:dyDescent="0.25">
-      <c r="A11" s="5"/>
-      <c r="B11" s="5"/>
-      <c r="C11" s="5"/>
+      <c r="A11" s="4"/>
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/docs/spec/ARM.xlsx
+++ b/docs/spec/ARM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\EitanKrimer\Documents\university\ADSS\ADSS_Group_Y\docs\spec\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBB33EFA-9F31-449B-B084-A44D2B0EBB48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFA440EB-89BC-47F9-B424-28900599CDD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ARM" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="47">
   <si>
     <t>ID</t>
   </si>
@@ -58,9 +58,6 @@
   </si>
   <si>
     <t>MH</t>
-  </si>
-  <si>
-    <t>NTH</t>
   </si>
   <si>
     <t>High</t>
@@ -521,7 +518,57 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Upon maximum truck weight overflow - the system will ask the </t>
+      <t xml:space="preserve">The </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="9" tint="-0.249977111117893"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>System</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> can not allow a </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="7" tint="-0.499984740745262"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>driver</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> without a sufficent drivers license type to drive any </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>truck</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">A </t>
     </r>
     <r>
       <rPr>
@@ -530,53 +577,16 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>TransportManager</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> which strategy to use:
-- </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="16"/>
-        <color rgb="FFE90505"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>cancel or change one of the destinations</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-- change truck
-- unload certain items from the current truck</t>
-    </r>
-  </si>
-  <si>
-    <t>Upon maximum truck weight overflow - the system will ask the TransportManager which strategy to use:
-- cancel or change one of the destinations
-- change truck
-- unload certain items from the current truck</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Don’t know what to do when
-"cancel or change one of the destinations" </t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">The </t>
+      <t>Transport Manager</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> in The </t>
     </r>
     <r>
       <rPr>
@@ -594,74 +604,6 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> can not allow a </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color theme="7" tint="-0.499984740745262"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>driver</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> without a sufficent drivers license type to drive any </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>truck</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">A </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF7030A0"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Transport Manager</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> in The </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color theme="9" tint="-0.249977111117893"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>System</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
       <t xml:space="preserve"> can define a variaty of </t>
     </r>
     <r>
@@ -702,20 +644,6 @@
       </rPr>
       <t xml:space="preserve"> of the different Transports.</t>
     </r>
-  </si>
-  <si>
-    <t>NTH or MH?</t>
-  </si>
-  <si>
-    <t>How to alert?</t>
-  </si>
-  <si>
-    <t>בנוגע ל "אחראי ההובלה"
-מי הוא אחראי ההובלה מבחינתך?
-האם מדובר במשתמש מערכת שמחליט ברגע יצירת הובלה את ההתנהלות המועדפת בעת חריגה?</t>
-  </si>
-  <si>
-    <t>???</t>
   </si>
   <si>
     <r>
@@ -817,6 +745,752 @@
   </si>
   <si>
     <r>
+      <t xml:space="preserve">The </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>System</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> must allow a </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>transport manager</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> to start a </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="5" tint="-0.249977111117893"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>transport</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="9" tint="-0.249977111117893"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>System</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> must allow a </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>transport manager</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> to create a future </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="5" tint="-0.249977111117893"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>transport</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>System</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> must allow a </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>transport manager</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> to update a </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="5" tint="-0.249977111117893"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>transport</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>System</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> must allow a </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>transport manager</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> to delete a </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="5" tint="-0.249977111117893"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>transport</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>System</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> must allow a </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>transport manager</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> a transport manager to create a </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="7" tint="-0.249977111117893"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>driver</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>System</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> must allow a </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>transport manager</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> to edit a </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="7" tint="-0.249977111117893"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>driver</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>System</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> must allow a </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>transport manager</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> to delete a </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="7" tint="-0.249977111117893"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>driver</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>System</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> must allow a </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>transport manager</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> to create a </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>truck</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>System</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> must allow a </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>transport manager</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> to edit a </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>truck</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>System</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> must allow a </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>transport manager</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> to delete a </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>truck</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>System</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> must allow a </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>admin</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> to create a </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>branch</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>System</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> must allow a </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>admin</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> to edit a </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>branch</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>System</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> must allow a </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>admin</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> to delete a </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>branch</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Upon maximum truck weight overflow - the system will ask the </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>TransportManager</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> which strategy to use:
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="16"/>
+        <color rgb="FFE90505"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>cancel or change one of the destinations</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+- change truck
+- unload certain items from the current truck
+(Basically give the option to edit the entire transport)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="9" tint="-0.249977111117893"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>System</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> must allow an </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>admin</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> to assign a user to the role of </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Transport Manager</t>
+    </r>
+  </si>
+  <si>
+    <r>
       <t xml:space="preserve">For any Transport in the System, a Transport should have:
 - Transport ID
 - planned datetime of transport
@@ -916,9 +1590,14 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve"> ID(s) (FK)
+- completed sources - List of Site(s) ID(s)
+- completed destinations - List of Site(s) ID(s)
 - actual start datetime
 - actual end datetime</t>
     </r>
+  </si>
+  <si>
+    <t>The system must allow to check for requested items at supplier - if they exist - in which suppliers</t>
   </si>
   <si>
     <r>
@@ -946,658 +1625,9 @@
 - site object FK
 - contact phone
 - contact name
+- site address
 - OPTIONAL Delivery File ID ( FK to actual Delivery File)
-- OPTIONAL Recroded weight at site</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">The </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>System</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> must allow a </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF7030A0"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>transport manager</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> to start a </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color theme="5" tint="-0.249977111117893"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>transport</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">The </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color theme="9" tint="-0.249977111117893"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>System</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> must allow a </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF7030A0"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>transport manager</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> to create a future </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color theme="5" tint="-0.249977111117893"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>transport</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">The </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>System</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> must allow a </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF7030A0"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>transport manager</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> to update a </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color theme="5" tint="-0.249977111117893"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>transport</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">The </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>System</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> must allow a </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF7030A0"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>transport manager</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> to delete a </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color theme="5" tint="-0.249977111117893"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>transport</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">The </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>System</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> must allow a </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF7030A0"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>transport manager</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> a transport manager to create a </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color theme="7" tint="-0.249977111117893"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>driver</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">The </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>System</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> must allow a </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF7030A0"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>transport manager</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> to edit a </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color theme="7" tint="-0.249977111117893"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>driver</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">The </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>System</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> must allow a </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF7030A0"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>transport manager</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> to delete a </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color theme="7" tint="-0.249977111117893"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>driver</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">The </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>System</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> must allow a </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF7030A0"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>transport manager</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> to create a </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>truck</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">The </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>System</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> must allow a </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF7030A0"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>transport manager</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> to edit a </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>truck</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">The </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>System</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> must allow a </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF7030A0"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>transport manager</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> to delete a </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>truck</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">The </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>System</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> must allow a </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF7030A0"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>admin</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> to create a </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>branch</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">The </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>System</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> must allow a </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF7030A0"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>admin</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> to edit a </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>branch</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">The </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>System</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> must allow a </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF7030A0"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>admin</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> to delete a </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>branch</t>
+- OPTIONAL Recorded weight at site</t>
     </r>
   </si>
 </sst>
@@ -1781,18 +1811,12 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -1891,7 +1915,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
@@ -1911,11 +1935,11 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
@@ -1937,12 +1961,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2232,7 +2250,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G70"/>
+  <dimension ref="A1:G72"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="21" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="2"/>
@@ -2253,7 +2271,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D1" s="9" t="s">
         <v>2</v>
@@ -2282,18 +2300,22 @@
         <v>1</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="D3" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G3" s="3" t="s">
         <v>14</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="E3" s="7"/>
-      <c r="F3" s="7"/>
-      <c r="G3" s="3" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="101.25" x14ac:dyDescent="0.25">
@@ -2302,22 +2324,22 @@
         <v>2</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>14</v>
-      </c>
       <c r="D4" s="5" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>6</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="162" x14ac:dyDescent="0.25">
@@ -2326,46 +2348,46 @@
         <v>3</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>14</v>
-      </c>
       <c r="D5" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>6</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="141.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
-        <f t="shared" ref="A6:A31" si="0">A5+1</f>
+        <f t="shared" ref="A6:A33" si="0">A5+1</f>
         <v>4</v>
       </c>
       <c r="B6" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>14</v>
-      </c>
       <c r="D6" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>6</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="141.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2374,46 +2396,46 @@
         <v>5</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>14</v>
-      </c>
       <c r="D7" s="5" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>6</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="222.75" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="243" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="B8" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>14</v>
-      </c>
       <c r="D8" s="5" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>6</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="140.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2422,46 +2444,46 @@
         <v>7</v>
       </c>
       <c r="B9" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="3" t="s">
-        <v>14</v>
-      </c>
       <c r="D9" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>6</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="342" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="B10" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>37</v>
+      <c r="D10" s="7" t="s">
+        <v>44</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>6</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="60.75" x14ac:dyDescent="0.25">
@@ -2470,22 +2492,22 @@
         <v>9</v>
       </c>
       <c r="B11" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C11" s="3" t="s">
-        <v>14</v>
-      </c>
       <c r="D11" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>6</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="101.25" x14ac:dyDescent="0.25">
@@ -2494,454 +2516,454 @@
         <v>10</v>
       </c>
       <c r="B12" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C12" s="3" t="s">
-        <v>14</v>
-      </c>
       <c r="D12" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>6</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="121.5" x14ac:dyDescent="0.25">
-      <c r="A13" s="16">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="81" x14ac:dyDescent="0.25">
+      <c r="A13" s="3">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="B13" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="C13" s="16" t="s">
-        <v>16</v>
-      </c>
-      <c r="D13" s="16" t="s">
-        <v>29</v>
-      </c>
-      <c r="E13" s="16" t="s">
+      <c r="B13" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F13" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F13" s="16" t="s">
-        <v>8</v>
-      </c>
-      <c r="G13" s="16" t="s">
+      <c r="G13" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="60.75" x14ac:dyDescent="0.25">
+      <c r="A14" s="3">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C14" s="8" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="14" spans="1:7" ht="60.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="17">
-        <f t="shared" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D14" s="17" t="s">
-        <v>40</v>
+      <c r="D14" s="3" t="s">
+        <v>43</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>6</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="60.75" x14ac:dyDescent="0.25">
-      <c r="A15" s="17">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="121.5" x14ac:dyDescent="0.25">
+      <c r="A15" s="3">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D15" s="17" t="s">
-        <v>39</v>
-      </c>
-      <c r="E15" s="3" t="s">
+      <c r="B15" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E15" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="F15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>15</v>
+      <c r="F15" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="G15" s="8" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="60.75" x14ac:dyDescent="0.25">
-      <c r="A16" s="17">
+      <c r="A16" s="8">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D16" s="17" t="s">
-        <v>41</v>
+        <v>15</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>30</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>6</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="60.75" x14ac:dyDescent="0.25">
-      <c r="A17" s="17">
+      <c r="A17" s="8">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D17" s="17" t="s">
-        <v>42</v>
+        <v>15</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>29</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>6</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="60.75" x14ac:dyDescent="0.25">
-      <c r="A18" s="17">
+      <c r="A18" s="8">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D18" s="17" t="s">
-        <v>43</v>
+        <v>15</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>31</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>6</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="60.75" x14ac:dyDescent="0.25">
-      <c r="A19" s="17">
+      <c r="A19" s="8">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D19" s="17" t="s">
-        <v>44</v>
+        <v>15</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>32</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>6</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="60.75" x14ac:dyDescent="0.25">
-      <c r="A20" s="17">
+      <c r="A20" s="8">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D20" s="17" t="s">
-        <v>45</v>
+        <v>15</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>33</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>6</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="60.75" x14ac:dyDescent="0.25">
-      <c r="A21" s="17">
+      <c r="A21" s="8">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D21" s="17" t="s">
-        <v>46</v>
+        <v>15</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>34</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>6</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="60.75" x14ac:dyDescent="0.25">
-      <c r="A22" s="17">
+      <c r="A22" s="8">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D22" s="17" t="s">
-        <v>47</v>
+        <v>15</v>
+      </c>
+      <c r="D22" s="8" t="s">
+        <v>35</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>6</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="60.75" x14ac:dyDescent="0.25">
-      <c r="A23" s="17">
+      <c r="A23" s="8">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D23" s="17" t="s">
-        <v>48</v>
+        <v>15</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>36</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>6</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="40.5" x14ac:dyDescent="0.25">
-      <c r="A24" s="17">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="60.75" x14ac:dyDescent="0.25">
+      <c r="A24" s="8">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D24" s="17" t="s">
-        <v>49</v>
+        <v>15</v>
+      </c>
+      <c r="D24" s="8" t="s">
+        <v>37</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>6</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" ht="40.5" x14ac:dyDescent="0.25">
-      <c r="A25" s="17">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="60.75" x14ac:dyDescent="0.25">
+      <c r="A25" s="8">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D25" s="17" t="s">
-        <v>50</v>
+        <v>15</v>
+      </c>
+      <c r="D25" s="8" t="s">
+        <v>38</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>6</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="40.5" x14ac:dyDescent="0.25">
-      <c r="A26" s="17">
+      <c r="A26" s="8">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D26" s="17" t="s">
-        <v>51</v>
+        <v>15</v>
+      </c>
+      <c r="D26" s="8" t="s">
+        <v>39</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>6</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G26" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="40.5" x14ac:dyDescent="0.25">
+      <c r="A27" s="8">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C27" s="3" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="27" spans="1:7" ht="141.75" x14ac:dyDescent="0.25">
-      <c r="A27" s="17">
-        <f>A23+1</f>
-        <v>22</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>18</v>
+      <c r="D27" s="8" t="s">
+        <v>40</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>6</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G27" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="40.5" x14ac:dyDescent="0.25">
+      <c r="A28" s="8">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C28" s="3" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="28" spans="1:7" ht="81" x14ac:dyDescent="0.25">
-      <c r="A28" s="3">
-        <f t="shared" si="0"/>
-        <v>23</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>19</v>
+      <c r="D28" s="8" t="s">
+        <v>41</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>6</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G28" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="141.75" x14ac:dyDescent="0.25">
+      <c r="A29" s="8">
+        <f>A25+1</f>
+        <v>24</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C29" s="3" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="29" spans="1:7" ht="81" x14ac:dyDescent="0.25">
-      <c r="A29" s="3">
-        <f t="shared" si="0"/>
-        <v>24</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="D29" s="3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>6</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" ht="182.25" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="81" x14ac:dyDescent="0.25">
       <c r="A30" s="3">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>6</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="81" x14ac:dyDescent="0.25">
@@ -2950,59 +2972,79 @@
         <v>26</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>6</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G31" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="222.75" x14ac:dyDescent="0.25">
+      <c r="A32" s="3">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C32" s="3" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="3">
-        <f t="shared" ref="A32:A34" si="1">A31+1</f>
-        <v>27</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C32" s="3"/>
-      <c r="D32" s="3"/>
-      <c r="E32" s="3"/>
-      <c r="F32" s="3"/>
-      <c r="G32" s="3"/>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D32" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="81" x14ac:dyDescent="0.25">
       <c r="A33" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>28</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C33" s="3"/>
-      <c r="D33" s="3"/>
-      <c r="E33" s="3"/>
-      <c r="F33" s="3"/>
-      <c r="G33" s="3"/>
+        <v>12</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="A34:A36" si="1">A33+1</f>
         <v>29</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C34" s="3"/>
       <c r="D34" s="3"/>
@@ -3012,11 +3054,11 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="3">
-        <f t="shared" ref="A35:A70" si="2">A34+1</f>
+        <f t="shared" si="1"/>
         <v>30</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C35" s="3"/>
       <c r="D35" s="3"/>
@@ -3026,11 +3068,11 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>31</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C36" s="3"/>
       <c r="D36" s="3"/>
@@ -3040,11 +3082,11 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="A37:A72" si="2">A36+1</f>
         <v>32</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C37" s="3"/>
       <c r="D37" s="3"/>
@@ -3058,7 +3100,7 @@
         <v>33</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C38" s="3"/>
       <c r="D38" s="3"/>
@@ -3072,7 +3114,7 @@
         <v>34</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C39" s="3"/>
       <c r="D39" s="3"/>
@@ -3086,7 +3128,7 @@
         <v>35</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C40" s="3"/>
       <c r="D40" s="3"/>
@@ -3100,7 +3142,7 @@
         <v>36</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C41" s="3"/>
       <c r="D41" s="3"/>
@@ -3114,7 +3156,7 @@
         <v>37</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C42" s="3"/>
       <c r="D42" s="3"/>
@@ -3128,7 +3170,7 @@
         <v>38</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C43" s="3"/>
       <c r="D43" s="3"/>
@@ -3142,7 +3184,7 @@
         <v>39</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C44" s="3"/>
       <c r="D44" s="3"/>
@@ -3156,7 +3198,7 @@
         <v>40</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C45" s="3"/>
       <c r="D45" s="3"/>
@@ -3170,7 +3212,7 @@
         <v>41</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C46" s="3"/>
       <c r="D46" s="3"/>
@@ -3184,7 +3226,7 @@
         <v>42</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C47" s="3"/>
       <c r="D47" s="3"/>
@@ -3198,7 +3240,7 @@
         <v>43</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C48" s="3"/>
       <c r="D48" s="3"/>
@@ -3212,7 +3254,7 @@
         <v>44</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C49" s="3"/>
       <c r="D49" s="3"/>
@@ -3226,7 +3268,7 @@
         <v>45</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C50" s="3"/>
       <c r="D50" s="3"/>
@@ -3240,7 +3282,7 @@
         <v>46</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C51" s="3"/>
       <c r="D51" s="3"/>
@@ -3254,7 +3296,7 @@
         <v>47</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C52" s="3"/>
       <c r="D52" s="3"/>
@@ -3268,7 +3310,7 @@
         <v>48</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C53" s="3"/>
       <c r="D53" s="3"/>
@@ -3282,7 +3324,7 @@
         <v>49</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C54" s="3"/>
       <c r="D54" s="3"/>
@@ -3296,7 +3338,7 @@
         <v>50</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C55" s="3"/>
       <c r="D55" s="3"/>
@@ -3310,7 +3352,7 @@
         <v>51</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C56" s="3"/>
       <c r="D56" s="3"/>
@@ -3324,7 +3366,7 @@
         <v>52</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C57" s="3"/>
       <c r="D57" s="3"/>
@@ -3338,7 +3380,7 @@
         <v>53</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C58" s="3"/>
       <c r="D58" s="3"/>
@@ -3352,7 +3394,7 @@
         <v>54</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C59" s="3"/>
       <c r="D59" s="3"/>
@@ -3366,7 +3408,7 @@
         <v>55</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C60" s="3"/>
       <c r="D60" s="3"/>
@@ -3380,7 +3422,7 @@
         <v>56</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C61" s="3"/>
       <c r="D61" s="3"/>
@@ -3394,7 +3436,7 @@
         <v>57</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C62" s="3"/>
       <c r="D62" s="3"/>
@@ -3408,7 +3450,7 @@
         <v>58</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C63" s="3"/>
       <c r="D63" s="3"/>
@@ -3422,7 +3464,7 @@
         <v>59</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C64" s="3"/>
       <c r="D64" s="3"/>
@@ -3436,7 +3478,7 @@
         <v>60</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C65" s="3"/>
       <c r="D65" s="3"/>
@@ -3450,7 +3492,7 @@
         <v>61</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C66" s="3"/>
       <c r="D66" s="3"/>
@@ -3464,7 +3506,7 @@
         <v>62</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C67" s="3"/>
       <c r="D67" s="3"/>
@@ -3478,7 +3520,7 @@
         <v>63</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C68" s="3"/>
       <c r="D68" s="3"/>
@@ -3492,7 +3534,7 @@
         <v>64</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C69" s="3"/>
       <c r="D69" s="3"/>
@@ -3506,13 +3548,41 @@
         <v>65</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C70" s="3"/>
       <c r="D70" s="3"/>
       <c r="E70" s="3"/>
       <c r="F70" s="3"/>
       <c r="G70" s="3"/>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A71" s="3">
+        <f t="shared" si="2"/>
+        <v>66</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C71" s="3"/>
+      <c r="D71" s="3"/>
+      <c r="E71" s="3"/>
+      <c r="F71" s="3"/>
+      <c r="G71" s="3"/>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A72" s="3">
+        <f t="shared" si="2"/>
+        <v>67</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C72" s="3"/>
+      <c r="D72" s="3"/>
+      <c r="E72" s="3"/>
+      <c r="F72" s="3"/>
+      <c r="G72" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -3539,7 +3609,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="21" x14ac:dyDescent="0.25">
       <c r="A1" s="13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B1" s="14"/>
       <c r="C1" s="15"/>
@@ -3549,58 +3619,42 @@
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="135" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>1</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="162" x14ac:dyDescent="0.25">
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+    </row>
+    <row r="4" spans="1:3" ht="21" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
         <f>A3+1</f>
         <v>2</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="101.25" x14ac:dyDescent="0.25">
+      <c r="B4" s="3"/>
+      <c r="C4" s="4"/>
+    </row>
+    <row r="5" spans="1:3" ht="21" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <f>A4+1</f>
         <v>3</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="168" x14ac:dyDescent="0.25">
+      <c r="B5" s="3"/>
+      <c r="C5" s="4"/>
+    </row>
+    <row r="6" spans="1:3" ht="21" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
         <f>A5+1</f>
         <v>4</v>
       </c>
-      <c r="B6" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>33</v>
-      </c>
+      <c r="B6" s="6"/>
+      <c r="C6" s="4"/>
     </row>
     <row r="7" spans="1:3" ht="21" x14ac:dyDescent="0.25">
       <c r="A7" s="4"/>

--- a/docs/spec/ARM.xlsx
+++ b/docs/spec/ARM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\EitanKrimer\Documents\university\ADSS\ADSS_Group_Y\docs\spec\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFA440EB-89BC-47F9-B424-28900599CDD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{574EEC38-4D4C-45EB-996D-9AF69A641C8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="16725" yWindow="0" windowWidth="12180" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ARM" sheetId="1" r:id="rId1"/>

--- a/docs/spec/ARM.xlsx
+++ b/docs/spec/ARM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\taoma\Downloads\תיכון ותכנון מערכות\ADSS_Group_Y\docs\spec\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5DEA2E3-5342-41FF-BCE9-B4FC3A2C66E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C4554CB-FC66-4CC4-96B3-7AE9CB56AE0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28935" yWindow="-75" windowWidth="29070" windowHeight="15750" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ARM" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="82">
   <si>
     <t>ID</t>
   </si>
@@ -240,153 +240,6 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve"> to receive the missing item(s).</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">When a </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color theme="5" tint="-0.249977111117893"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Transport</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> starts - the </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color theme="9" tint="-0.249977111117893"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>System</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> must change the </t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="16"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">status of the </t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="16"/>
-        <color theme="5" tint="-0.249977111117893"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Transport</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>(status + datetime of the start)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">In a given </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color theme="5" tint="-0.249977111117893"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Transport</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> the </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color theme="9" tint="-0.249977111117893"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>System</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> must know from which </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color theme="4" tint="-0.249977111117893"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>suppliers</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> to which </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FFA50021"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>branches</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> the supplies should be distribued.</t>
     </r>
   </si>
   <si>
@@ -512,85 +365,6 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">A </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF7030A0"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Transport Manager</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> in The </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color theme="9" tint="-0.249977111117893"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>System</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> can define a variaty of </t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="16"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>transport areas</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> - allowing the system to organize the </t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="16"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Trucks</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> of the different Transports.</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t xml:space="preserve">The System must follow this format for </t>
     </r>
     <r>
@@ -658,702 +432,6 @@
 - Branch name
 - Branch address
 - Branch phone</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">The </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>System</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> must allow a </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF7030A0"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>transport manager</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> to start a </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color theme="5" tint="-0.249977111117893"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>transport</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">The </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color theme="9" tint="-0.249977111117893"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>System</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> must allow a </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF7030A0"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>transport manager</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> to create a future </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color theme="5" tint="-0.249977111117893"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>transport</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">The </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>System</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> must allow a </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF7030A0"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>transport manager</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> to update a </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color theme="5" tint="-0.249977111117893"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>transport</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">The </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>System</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> must allow a </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF7030A0"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>transport manager</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> to delete a </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color theme="5" tint="-0.249977111117893"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>transport</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">The </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>System</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> must allow a </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF7030A0"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>transport manager</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> a transport manager to create a </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color theme="7" tint="-0.249977111117893"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>driver</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">The </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>System</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> must allow a </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF7030A0"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>transport manager</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> to edit a </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color theme="7" tint="-0.249977111117893"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>driver</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">The </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>System</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> must allow a </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF7030A0"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>transport manager</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> to delete a </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color theme="7" tint="-0.249977111117893"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>driver</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">The </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>System</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> must allow a </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF7030A0"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>transport manager</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> to create a </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>truck</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">The </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>System</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> must allow a </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF7030A0"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>transport manager</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> to edit a </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>truck</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">The </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>System</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> must allow a </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF7030A0"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>transport manager</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> to delete a </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>truck</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">The </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>System</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> must allow a </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF7030A0"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>admin</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> to create a </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>branch</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">The </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>System</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> must allow a </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF7030A0"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>admin</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> to edit a </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>branch</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">The </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>System</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> must allow a </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF7030A0"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>admin</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> to delete a </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>branch</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Upon maximum truck weight overflow - the system will ask the </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF7030A0"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>TransportManager</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> which strategy to use:
-- </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="16"/>
-        <color rgb="FFE90505"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>cancel or change one of the destinations</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-- change truck
-- unload certain items from the current truck
-(Basically give the option to edit the entire transport)</t>
     </r>
   </si>
   <si>
@@ -1715,12 +793,1791 @@
 - Delivery File ID (FK)</t>
     </r>
   </si>
+  <si>
+    <t>NTH</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">In a given </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="5" tint="-0.249977111117893"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Transport</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> the </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="9" tint="-0.249977111117893"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>System</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> must know from which </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="4" tint="-0.249977111117893"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>suppliers</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> to which </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FFA50021"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>branches</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> the supplies should be distribued, via </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="0" tint="-0.34998626667073579"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>TransportRoute</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="9" tint="-0.249977111117893"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>System</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> must allow a </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>transport manager/user</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> to create a future </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="5" tint="-0.249977111117893"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>transport</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>System</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> must allow a </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>transport manager/user</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> to update a </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="5" tint="-0.249977111117893"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>transport</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="9" tint="-0.249977111117893"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>System</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> must allow to define a user as </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">transport manager </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>System</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> must allow a </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>transport manager/user</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> to delete a </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="5" tint="-0.249977111117893"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>transport</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>System</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> must allow a </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>transport manager/user</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> a transport manager to create a </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="7" tint="-0.249977111117893"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>driver</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>System</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> must allow a </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>transport manager/user</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> to edit a </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="7" tint="-0.249977111117893"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>driver</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>System</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> must allow a </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>transport manager/user</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> to delete a </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="7" tint="-0.249977111117893"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>driver</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>System</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> must allow a </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>transport manager/user</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> to create a </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>truck</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>System</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> must allow a </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>transport manager/user</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> to edit a </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>truck</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>System</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> must allow a </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>transport manager/user</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> to delete a </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>truck</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="9" tint="-0.249977111117893"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>System</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> must allow to define a user as </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>admin</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>System</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> must allow a </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>admin/user</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> to create a </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>branch</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>System</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> must allow a </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>admin/user</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> to edit a </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>branch</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>System</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> must allow a </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>admin/user</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> to delete a </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>branch</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">When a </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="5" tint="-0.249977111117893"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Transport</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> starts - the </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="9" tint="-0.249977111117893"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>System</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> must change the </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">status of the </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="16"/>
+        <color theme="5" tint="-0.249977111117893"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Transport</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>(status + datetime of the start), in all the Transport routes that connected to it.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Upon maximum truck weight overflow - the system will ask the </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>TransportManager/user</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> which strategy to use:
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="16"/>
+        <color rgb="FFE90505"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>cancel or change one of the destinations</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+- change truck
+- unload certain items from the current truck
+(Basically give the option to edit the entire transport)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>System</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> must allow a </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>admin/user</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> to create a </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="2" tint="-0.749992370372631"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>TransportArea</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>System</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> must allow a </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>admin/user</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> to edit a </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="2" tint="-0.749992370372631"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>TransportArea</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>System</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> must allow a </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>admin/user</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> to delete a </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="2" tint="-0.749992370372631"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>TransportArea</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="9" tint="-0.249977111117893"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>System</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> should have show all the </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="5"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Transport</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> by ID in the </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="9"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>System</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="9"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>System</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> have to allow to destination source of </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="5"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Transport</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1" tint="0.14999847407452621"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Transport's route</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="9"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>System</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> have to allow to Visit source of </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="5"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Transport</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1" tint="0.14999847407452621"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Transport's route</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="9"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>System</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> have to Print the next drive for driver</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="9"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>System</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> have to Print transport drives for driver - by Transport ID</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="9" tint="-0.249977111117893"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>System</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> have to show all the </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="2" tint="-0.749992370372631"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">TransportAreas </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">in the </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="9"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>System</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="9" tint="-0.249977111117893"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>System</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> have to have show all the </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="5"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Transport</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> in the </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="9"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>System</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="9" tint="-0.249977111117893"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>System</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> have to show the TransportArea by ID</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="9"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>System</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> have to allow to Unstart </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="5"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Transport</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1" tint="0.14999847407452621"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Transport's route</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="9"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>System</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> have to show </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>truck</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> by its ID</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="9"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>System</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> have to show all the  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>trucks</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> in the </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="9"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>System</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="9"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>System</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> have to show </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="7" tint="-0.249977111117893"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>drivers</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> by its ID</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="9"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>System</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> have to show </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>branch</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> by its ID</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="9"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>System</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> have to show all the </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="7" tint="-0.249977111117893"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>drivers</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> in the </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="9"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>System</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="9"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>System</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> have to show  all the </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>branch</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> in the </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="9"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>System</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">F </t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="9"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>System</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> have to show gui for handle all the models</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="9"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>System</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> have to load/unload by the chioce of the </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>user</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> mock values (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>only</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> for this version)</t>
+    </r>
+  </si>
+  <si>
+    <t>Transport Managar</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>How to define the transport manager?</t>
+  </si>
+  <si>
+    <t>Trucks  weight</t>
+  </si>
+  <si>
+    <t>who and how to insert the weight to the system?</t>
+  </si>
+  <si>
+    <t>Transport area</t>
+  </si>
+  <si>
+    <t>who is the responsiable to define the transports areas?</t>
+  </si>
+  <si>
+    <t>TransportIssue</t>
+  </si>
+  <si>
+    <t>how to define in which cases we use unload trucks, etc.</t>
+  </si>
+  <si>
+    <t>on which cases we should cancel the transport</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="31" x14ac:knownFonts="1">
+  <fonts count="37" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1912,6 +2769,43 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1" tint="0.14999847407452621"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="0" tint="-0.34998626667073579"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="9"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="2" tint="-0.749992370372631"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="5"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -2023,7 +2917,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
@@ -2049,6 +2943,12 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
@@ -2061,20 +2961,20 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
+    <xf numFmtId="20" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2364,7 +3264,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H73"/>
+  <dimension ref="A1:H76"/>
   <sheetFormatPr defaultColWidth="9.09765625" defaultRowHeight="20.399999999999999" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.09765625" style="2"/>
@@ -2377,39 +3277,39 @@
     <col min="8" max="16384" width="9.09765625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:7" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="G1" s="11" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="10"/>
-      <c r="B2" s="10"/>
-      <c r="C2" s="12"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
-    </row>
-    <row r="3" spans="1:8" ht="123" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="12"/>
+      <c r="B2" s="12"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="12"/>
+      <c r="G2" s="12"/>
+    </row>
+    <row r="3" spans="1:7" ht="123" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>1</v>
       </c>
@@ -2420,7 +3320,7 @@
         <v>13</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>6</v>
@@ -2432,7 +3332,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="102.6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="102.6" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <f>A3+1</f>
         <v>2</v>
@@ -2444,7 +3344,7 @@
         <v>13</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>6</v>
@@ -2456,7 +3356,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="163.19999999999999" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="163.19999999999999" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <f>A4+1</f>
         <v>3</v>
@@ -2468,7 +3368,7 @@
         <v>13</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>6</v>
@@ -2480,9 +3380,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="207.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="207.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
-        <f t="shared" ref="A6:A34" si="0">A5+1</f>
+        <f t="shared" ref="A6:A37" si="0">A5+1</f>
         <v>4</v>
       </c>
       <c r="B6" s="3" t="s">
@@ -2492,7 +3392,7 @@
         <v>13</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>6</v>
@@ -2504,7 +3404,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="178.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="178.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -2516,7 +3416,7 @@
         <v>13</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>6</v>
@@ -2528,7 +3428,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="198.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="198.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -2540,7 +3440,7 @@
         <v>13</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>6</v>
@@ -2552,7 +3452,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="226.8" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="226.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -2564,7 +3464,7 @@
         <v>13</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>6</v>
@@ -2576,7 +3476,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="343.8" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="343.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <f>A9+1</f>
         <v>8</v>
@@ -2588,7 +3488,7 @@
         <v>13</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>6</v>
@@ -2600,7 +3500,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="142.19999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="142.19999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>9</v>
       </c>
@@ -2611,22 +3511,19 @@
         <v>13</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F11" s="17" t="s">
+      <c r="F11" s="10" t="s">
         <v>7</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="H11" s="16" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="61.2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="12" spans="1:7" ht="61.2" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <v>10</v>
       </c>
@@ -2649,7 +3546,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="81.599999999999994" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="102" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -2661,7 +3558,7 @@
         <v>13</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>6</v>
@@ -2673,7 +3570,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="61.2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="61.2" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -2685,19 +3582,19 @@
         <v>15</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="61.2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="61.2" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -2709,45 +3606,43 @@
         <v>15</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="F15" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="64.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="8">
+        <v>14</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F16" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="G15" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="102" x14ac:dyDescent="0.25">
-      <c r="A16" s="3">
-        <f t="shared" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="B16" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C16" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="D16" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="E16" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="F16" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="G16" s="8" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="61.2" x14ac:dyDescent="0.25">
+      <c r="G16" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="64.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="8">
-        <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="B17" s="3" t="s">
@@ -2757,10 +3652,10 @@
         <v>15</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>7</v>
@@ -2771,7 +3666,6 @@
     </row>
     <row r="18" spans="1:7" ht="61.2" x14ac:dyDescent="0.25">
       <c r="A18" s="8">
-        <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="B18" s="3" t="s">
@@ -2781,7 +3675,7 @@
         <v>15</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>6</v>
@@ -2795,7 +3689,6 @@
     </row>
     <row r="19" spans="1:7" ht="61.2" x14ac:dyDescent="0.25">
       <c r="A19" s="8">
-        <f t="shared" si="0"/>
         <v>17</v>
       </c>
       <c r="B19" s="3" t="s">
@@ -2805,7 +3698,7 @@
         <v>15</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>6</v>
@@ -2829,7 +3722,7 @@
         <v>15</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>6</v>
@@ -2841,7 +3734,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="61.2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="81.599999999999994" x14ac:dyDescent="0.25">
       <c r="A21" s="8">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -2853,7 +3746,7 @@
         <v>15</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>6</v>
@@ -2865,7 +3758,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="40.799999999999997" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" ht="61.2" x14ac:dyDescent="0.25">
       <c r="A22" s="8">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -2877,7 +3770,7 @@
         <v>15</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>6</v>
@@ -2901,7 +3794,7 @@
         <v>15</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>6</v>
@@ -2925,7 +3818,7 @@
         <v>15</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>6</v>
@@ -2937,7 +3830,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="40.799999999999997" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" ht="61.2" x14ac:dyDescent="0.25">
       <c r="A25" s="8">
         <f t="shared" si="0"/>
         <v>23</v>
@@ -2949,7 +3842,7 @@
         <v>15</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>6</v>
@@ -2973,7 +3866,7 @@
         <v>15</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>6</v>
@@ -2997,7 +3890,7 @@
         <v>15</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>6</v>
@@ -3021,7 +3914,7 @@
         <v>15</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>6</v>
@@ -3045,7 +3938,7 @@
         <v>15</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>6</v>
@@ -3057,10 +3950,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="142.80000000000001" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" ht="61.2" x14ac:dyDescent="0.25">
       <c r="A30" s="8">
-        <f>A26+1</f>
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>12</v>
@@ -3068,8 +3960,8 @@
       <c r="C30" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D30" s="3" t="s">
-        <v>17</v>
+      <c r="D30" s="8" t="s">
+        <v>51</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>6</v>
@@ -3081,10 +3973,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="81.599999999999994" x14ac:dyDescent="0.25">
-      <c r="A31" s="3">
-        <f t="shared" si="0"/>
-        <v>26</v>
+    <row r="31" spans="1:7" ht="61.2" x14ac:dyDescent="0.25">
+      <c r="A31" s="8">
+        <v>30</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>12</v>
@@ -3092,8 +3983,8 @@
       <c r="C31" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D31" s="3" t="s">
-        <v>18</v>
+      <c r="D31" s="8" t="s">
+        <v>52</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>6</v>
@@ -3106,9 +3997,8 @@
       </c>
     </row>
     <row r="32" spans="1:7" ht="61.2" x14ac:dyDescent="0.25">
-      <c r="A32" s="3">
-        <f t="shared" si="0"/>
-        <v>27</v>
+      <c r="A32" s="8">
+        <v>31</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>12</v>
@@ -3116,8 +4006,8 @@
       <c r="C32" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>21</v>
+      <c r="D32" s="8" t="s">
+        <v>53</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>6</v>
@@ -3129,10 +4019,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="225.6" x14ac:dyDescent="0.25">
-      <c r="A33" s="3">
-        <f t="shared" si="0"/>
-        <v>28</v>
+    <row r="33" spans="1:8" ht="142.80000000000001" x14ac:dyDescent="0.25">
+      <c r="A33" s="8">
+        <v>32</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>12</v>
@@ -3141,10 +4030,10 @@
         <v>15</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="F33" s="3" t="s">
         <v>7</v>
@@ -3153,10 +4042,10 @@
         <v>14</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="61.2" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" ht="122.4" x14ac:dyDescent="0.25">
       <c r="A34" s="3">
         <f t="shared" si="0"/>
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>12</v>
@@ -3165,10 +4054,10 @@
         <v>15</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>22</v>
+        <v>49</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="F34" s="3" t="s">
         <v>7</v>
@@ -3177,290 +4066,493 @@
         <v>14</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" ht="61.2" x14ac:dyDescent="0.25">
       <c r="A35" s="3">
-        <f t="shared" ref="A35:A37" si="1">A34+1</f>
-        <v>30</v>
+        <f t="shared" si="0"/>
+        <v>34</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C35" s="3"/>
-      <c r="D35" s="3"/>
-      <c r="E35" s="3"/>
-      <c r="F35" s="3"/>
-      <c r="G35" s="3"/>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C35" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" ht="225.6" x14ac:dyDescent="0.25">
       <c r="A36" s="3">
+        <f t="shared" si="0"/>
+        <v>35</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" ht="61.2" x14ac:dyDescent="0.25">
+      <c r="A37" s="3">
+        <f t="shared" si="0"/>
+        <v>36</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" ht="40.799999999999997" x14ac:dyDescent="0.25">
+      <c r="A38" s="3">
+        <f t="shared" ref="A38:A40" si="1">A37+1</f>
+        <v>37</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" ht="40.799999999999997" x14ac:dyDescent="0.25">
+      <c r="A39" s="3">
         <f t="shared" si="1"/>
-        <v>31</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C36" s="3"/>
-      <c r="D36" s="3"/>
-      <c r="E36" s="3"/>
-      <c r="F36" s="3"/>
-      <c r="G36" s="3"/>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="3">
+        <v>38</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" ht="40.799999999999997" x14ac:dyDescent="0.25">
+      <c r="A40" s="3">
         <f t="shared" si="1"/>
-        <v>32</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C37" s="3"/>
-      <c r="D37" s="3"/>
-      <c r="E37" s="3"/>
-      <c r="F37" s="3"/>
-      <c r="G37" s="3"/>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="3">
-        <f t="shared" ref="A38:A73" si="2">A37+1</f>
-        <v>33</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C38" s="3"/>
-      <c r="D38" s="3"/>
-      <c r="E38" s="3"/>
-      <c r="F38" s="3"/>
-      <c r="G38" s="3"/>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="3">
-        <f t="shared" si="2"/>
-        <v>34</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C39" s="3"/>
-      <c r="D39" s="3"/>
-      <c r="E39" s="3"/>
-      <c r="F39" s="3"/>
-      <c r="G39" s="3"/>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="3">
-        <f t="shared" si="2"/>
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C40" s="3"/>
-      <c r="D40" s="3"/>
-      <c r="E40" s="3"/>
-      <c r="F40" s="3"/>
-      <c r="G40" s="3"/>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C40" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" ht="40.799999999999997" x14ac:dyDescent="0.25">
       <c r="A41" s="3">
-        <f t="shared" si="2"/>
-        <v>36</v>
+        <f t="shared" ref="A41:A76" si="2">A40+1</f>
+        <v>40</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C41" s="3"/>
-      <c r="D41" s="3"/>
-      <c r="E41" s="3"/>
-      <c r="F41" s="3"/>
-      <c r="G41" s="3"/>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C41" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" ht="61.2" x14ac:dyDescent="0.25">
       <c r="A42" s="3">
         <f t="shared" si="2"/>
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B42" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C42" s="3"/>
-      <c r="D42" s="3"/>
-      <c r="E42" s="3"/>
-      <c r="F42" s="3"/>
-      <c r="G42" s="3"/>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C42" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F42" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" ht="40.799999999999997" x14ac:dyDescent="0.25">
       <c r="A43" s="3">
         <f t="shared" si="2"/>
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B43" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C43" s="3"/>
-      <c r="D43" s="3"/>
-      <c r="E43" s="3"/>
-      <c r="F43" s="3"/>
-      <c r="G43" s="3"/>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C43" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H43" s="9" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" ht="61.2" x14ac:dyDescent="0.25">
       <c r="A44" s="3">
         <f t="shared" si="2"/>
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C44" s="3"/>
-      <c r="D44" s="3"/>
-      <c r="E44" s="3"/>
-      <c r="F44" s="3"/>
-      <c r="G44" s="3"/>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C44" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" ht="61.2" x14ac:dyDescent="0.25">
       <c r="A45" s="3">
         <f t="shared" si="2"/>
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C45" s="3"/>
-      <c r="D45" s="3"/>
-      <c r="E45" s="3"/>
-      <c r="F45" s="3"/>
-      <c r="G45" s="3"/>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C45" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" ht="61.2" x14ac:dyDescent="0.25">
       <c r="A46" s="3">
         <f t="shared" si="2"/>
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C46" s="3"/>
-      <c r="D46" s="3"/>
-      <c r="E46" s="3"/>
-      <c r="F46" s="3"/>
-      <c r="G46" s="3"/>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C46" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" ht="40.799999999999997" x14ac:dyDescent="0.25">
       <c r="A47" s="3">
         <f t="shared" si="2"/>
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B47" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C47" s="3"/>
-      <c r="D47" s="3"/>
-      <c r="E47" s="3"/>
-      <c r="F47" s="3"/>
-      <c r="G47" s="3"/>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C47" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" ht="40.799999999999997" x14ac:dyDescent="0.25">
       <c r="A48" s="3">
         <f t="shared" si="2"/>
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B48" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C48" s="3"/>
-      <c r="D48" s="3"/>
-      <c r="E48" s="3"/>
-      <c r="F48" s="3"/>
-      <c r="G48" s="3"/>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C48" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" ht="40.799999999999997" x14ac:dyDescent="0.25">
       <c r="A49" s="3">
         <f t="shared" si="2"/>
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B49" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C49" s="3"/>
-      <c r="D49" s="3"/>
-      <c r="E49" s="3"/>
-      <c r="F49" s="3"/>
-      <c r="G49" s="3"/>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C49" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" ht="40.799999999999997" x14ac:dyDescent="0.25">
       <c r="A50" s="3">
         <f t="shared" si="2"/>
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B50" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C50" s="3"/>
-      <c r="D50" s="3"/>
-      <c r="E50" s="3"/>
-      <c r="F50" s="3"/>
-      <c r="G50" s="3"/>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C50" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F50" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G50" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" ht="40.799999999999997" x14ac:dyDescent="0.25">
       <c r="A51" s="3">
         <f t="shared" si="2"/>
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B51" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C51" s="3"/>
-      <c r="D51" s="3"/>
-      <c r="E51" s="3"/>
-      <c r="F51" s="3"/>
-      <c r="G51" s="3"/>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C51" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="E51" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F51" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G51" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" ht="40.799999999999997" x14ac:dyDescent="0.25">
       <c r="A52" s="3">
         <f t="shared" si="2"/>
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B52" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C52" s="3"/>
-      <c r="D52" s="3"/>
-      <c r="E52" s="3"/>
-      <c r="F52" s="3"/>
-      <c r="G52" s="3"/>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C52" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" ht="40.799999999999997" x14ac:dyDescent="0.25">
       <c r="A53" s="3">
         <f t="shared" si="2"/>
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B53" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C53" s="3"/>
-      <c r="D53" s="3"/>
-      <c r="E53" s="3"/>
-      <c r="F53" s="3"/>
-      <c r="G53" s="3"/>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C53" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="E53" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F53" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G53" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" ht="61.8" x14ac:dyDescent="0.25">
       <c r="A54" s="3">
         <f t="shared" si="2"/>
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B54" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C54" s="3"/>
-      <c r="D54" s="3"/>
-      <c r="E54" s="3"/>
-      <c r="F54" s="3"/>
-      <c r="G54" s="3"/>
+      <c r="C54" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F54" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="3">
         <f t="shared" si="2"/>
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B55" s="3" t="s">
         <v>12</v>
@@ -3474,7 +4566,7 @@
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="3">
         <f t="shared" si="2"/>
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B56" s="3" t="s">
         <v>12</v>
@@ -3488,7 +4580,7 @@
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="3">
         <f t="shared" si="2"/>
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B57" s="3" t="s">
         <v>12</v>
@@ -3502,7 +4594,7 @@
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="3">
         <f t="shared" si="2"/>
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B58" s="3" t="s">
         <v>12</v>
@@ -3516,7 +4608,7 @@
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" s="3">
         <f t="shared" si="2"/>
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="B59" s="3" t="s">
         <v>12</v>
@@ -3530,7 +4622,7 @@
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" s="3">
         <f t="shared" si="2"/>
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="B60" s="3" t="s">
         <v>12</v>
@@ -3544,7 +4636,7 @@
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" s="3">
         <f t="shared" si="2"/>
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="B61" s="3" t="s">
         <v>12</v>
@@ -3558,7 +4650,7 @@
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" s="3">
         <f t="shared" si="2"/>
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="B62" s="3" t="s">
         <v>12</v>
@@ -3572,7 +4664,7 @@
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" s="3">
         <f t="shared" si="2"/>
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B63" s="3" t="s">
         <v>12</v>
@@ -3586,7 +4678,7 @@
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" s="3">
         <f t="shared" si="2"/>
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="B64" s="3" t="s">
         <v>12</v>
@@ -3600,7 +4692,7 @@
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" s="3">
         <f t="shared" si="2"/>
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="B65" s="3" t="s">
         <v>12</v>
@@ -3614,7 +4706,7 @@
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" s="3">
         <f t="shared" si="2"/>
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="B66" s="3" t="s">
         <v>12</v>
@@ -3628,7 +4720,7 @@
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="3">
         <f t="shared" si="2"/>
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B67" s="3" t="s">
         <v>12</v>
@@ -3642,7 +4734,7 @@
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" s="3">
         <f t="shared" si="2"/>
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B68" s="3" t="s">
         <v>12</v>
@@ -3656,7 +4748,7 @@
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" s="3">
         <f t="shared" si="2"/>
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="B69" s="3" t="s">
         <v>12</v>
@@ -3670,7 +4762,7 @@
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" s="3">
         <f t="shared" si="2"/>
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B70" s="3" t="s">
         <v>12</v>
@@ -3684,7 +4776,7 @@
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" s="3">
         <f t="shared" si="2"/>
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B71" s="3" t="s">
         <v>12</v>
@@ -3698,7 +4790,7 @@
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" s="3">
         <f t="shared" si="2"/>
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="B72" s="3" t="s">
         <v>12</v>
@@ -3712,7 +4804,7 @@
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" s="3">
         <f t="shared" si="2"/>
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="B73" s="3" t="s">
         <v>12</v>
@@ -3722,6 +4814,48 @@
       <c r="E73" s="3"/>
       <c r="F73" s="3"/>
       <c r="G73" s="3"/>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A74" s="3">
+        <f t="shared" si="2"/>
+        <v>73</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C74" s="3"/>
+      <c r="D74" s="3"/>
+      <c r="E74" s="3"/>
+      <c r="F74" s="3"/>
+      <c r="G74" s="3"/>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A75" s="3">
+        <f t="shared" si="2"/>
+        <v>74</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C75" s="3"/>
+      <c r="D75" s="3"/>
+      <c r="E75" s="3"/>
+      <c r="F75" s="3"/>
+      <c r="G75" s="3"/>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A76" s="3">
+        <f t="shared" si="2"/>
+        <v>75</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C76" s="3"/>
+      <c r="D76" s="3"/>
+      <c r="E76" s="3"/>
+      <c r="F76" s="3"/>
+      <c r="G76" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -3740,21 +4874,22 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6A548FC-132A-4BCF-B26C-A9E84109E40A}">
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="30" customWidth="1"/>
     <col min="3" max="3" width="34.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
+    <row r="1" spans="1:4" ht="20.399999999999999" x14ac:dyDescent="0.25">
+      <c r="A1" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="15"/>
-    </row>
-    <row r="2" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+      <c r="B1" s="17"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="19"/>
+    </row>
+    <row r="2" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -3764,59 +4899,88 @@
       <c r="C2" s="1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+      <c r="D2" s="19"/>
+    </row>
+    <row r="3" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>1</v>
       </c>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-    </row>
-    <row r="4" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A4" s="4">
+      <c r="B3" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D3" s="19" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="40.799999999999997" x14ac:dyDescent="0.25">
+      <c r="A4" s="6">
         <f>A3+1</f>
         <v>2</v>
       </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="4"/>
-    </row>
-    <row r="5" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A5" s="4">
+      <c r="B4" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="D4" s="19"/>
+    </row>
+    <row r="5" spans="1:4" ht="61.2" x14ac:dyDescent="0.25">
+      <c r="A5" s="6">
         <f>A4+1</f>
         <v>3</v>
       </c>
-      <c r="B5" s="3"/>
-      <c r="C5" s="4"/>
-    </row>
-    <row r="6" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A6" s="4">
+      <c r="B5" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="D5" s="19"/>
+    </row>
+    <row r="6" spans="1:4" ht="61.2" x14ac:dyDescent="0.25">
+      <c r="A6" s="6">
         <f>A5+1</f>
         <v>4</v>
       </c>
-      <c r="B6" s="6"/>
-      <c r="C6" s="4"/>
-    </row>
-    <row r="7" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A7" s="4"/>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-    </row>
-    <row r="8" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.25">
+      <c r="B6" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="D6" s="19"/>
+    </row>
+    <row r="7" spans="1:4" ht="40.799999999999997" x14ac:dyDescent="0.25">
+      <c r="A7" s="4">
+        <v>5</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="20.399999999999999" x14ac:dyDescent="0.25">
       <c r="A8" s="4"/>
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
     </row>
-    <row r="9" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" ht="20.399999999999999" x14ac:dyDescent="0.25">
       <c r="A9" s="4"/>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
     </row>
-    <row r="10" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" ht="20.399999999999999" x14ac:dyDescent="0.25">
       <c r="A10" s="4"/>
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
     </row>
-    <row r="11" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" ht="20.399999999999999" x14ac:dyDescent="0.25">
       <c r="A11" s="4"/>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>

--- a/docs/spec/ARM.xlsx
+++ b/docs/spec/ARM.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\taoma\Downloads\תיכון ותכנון מערכות\ADSS_Group_Y\docs\spec\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\EitanKrimer\Documents\university\ADSS\ADSS_Group_Y\docs\spec\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C4554CB-FC66-4CC4-96B3-7AE9CB56AE0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAAB8A9D-C85D-46D8-8A5D-2F6A409DCB27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="1800" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ARM" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="81">
   <si>
     <t>ID</t>
   </si>
@@ -601,9 +601,6 @@
 - Unloaded Items Delivery File ID
 - Transport route ID </t>
     </r>
-  </si>
-  <si>
-    <t>הגעתי עד פה</t>
   </si>
   <si>
     <r>
@@ -2581,7 +2578,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -2600,7 +2597,7 @@
     <font>
       <sz val="16"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -2807,7 +2804,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2817,12 +2814,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2943,11 +2934,14 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
@@ -2961,9 +2955,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="20" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -2973,8 +2964,8 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3265,51 +3256,51 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H76"/>
-  <sheetFormatPr defaultColWidth="9.09765625" defaultRowHeight="20.399999999999999" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="21" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.09765625" style="2"/>
-    <col min="2" max="2" width="15.3984375" style="2" customWidth="1"/>
+    <col min="1" max="1" width="9.140625" style="2"/>
+    <col min="2" max="2" width="15.42578125" style="2" customWidth="1"/>
     <col min="3" max="3" width="10" style="2" customWidth="1"/>
-    <col min="4" max="4" width="43.59765625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="12.09765625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="9.09765625" style="2"/>
-    <col min="7" max="7" width="26.296875" style="2" customWidth="1"/>
-    <col min="8" max="16384" width="9.09765625" style="2"/>
+    <col min="4" max="4" width="43.5703125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="12.140625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="9.140625" style="2"/>
+    <col min="7" max="7" width="26.28515625" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="D1" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="E1" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="F1" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="11" t="s">
+      <c r="G1" s="12" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="12"/>
-      <c r="B2" s="12"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="12"/>
-      <c r="E2" s="12"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="12"/>
-    </row>
-    <row r="3" spans="1:7" ht="123" x14ac:dyDescent="0.25">
+      <c r="A2" s="13"/>
+      <c r="B2" s="13"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+    </row>
+    <row r="3" spans="1:7" ht="121.5" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>1</v>
       </c>
@@ -3332,7 +3323,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="102.6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="101.25" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <f>A3+1</f>
         <v>2</v>
@@ -3356,7 +3347,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="163.19999999999999" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="162" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <f>A4+1</f>
         <v>3</v>
@@ -3404,7 +3395,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="178.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="178.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -3452,7 +3443,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="226.8" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="226.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -3476,7 +3467,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="343.8" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="343.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <f>A9+1</f>
         <v>8</v>
@@ -3488,7 +3479,7 @@
         <v>13</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>6</v>
@@ -3500,7 +3491,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="142.19999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="142.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>9</v>
       </c>
@@ -3511,19 +3502,19 @@
         <v>13</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F11" s="10" t="s">
+      <c r="F11" s="9" t="s">
         <v>7</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="61.2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="60.75" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <v>10</v>
       </c>
@@ -3546,7 +3537,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="102" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="101.25" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -3558,7 +3549,7 @@
         <v>13</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>6</v>
@@ -3570,7 +3561,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="61.2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="81" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -3585,16 +3576,16 @@
         <v>24</v>
       </c>
       <c r="E14" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F14" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>33</v>
-      </c>
       <c r="G14" s="3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="61.2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="60.75" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -3609,16 +3600,16 @@
         <v>23</v>
       </c>
       <c r="E15" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F15" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="F15" s="3" t="s">
-        <v>33</v>
-      </c>
       <c r="G15" s="3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="64.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="64.150000000000006" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="8">
         <v>14</v>
       </c>
@@ -3629,10 +3620,10 @@
         <v>15</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F16" s="3" t="s">
         <v>7</v>
@@ -3641,7 +3632,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="64.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="64.150000000000006" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="8">
         <v>15</v>
       </c>
@@ -3652,10 +3643,10 @@
         <v>15</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>7</v>
@@ -3664,7 +3655,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="61.2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="60.75" x14ac:dyDescent="0.25">
       <c r="A18" s="8">
         <v>16</v>
       </c>
@@ -3675,7 +3666,7 @@
         <v>15</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>6</v>
@@ -3687,7 +3678,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="61.2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="60.75" x14ac:dyDescent="0.25">
       <c r="A19" s="8">
         <v>17</v>
       </c>
@@ -3698,7 +3689,7 @@
         <v>15</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>6</v>
@@ -3710,7 +3701,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="61.2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="60.75" x14ac:dyDescent="0.25">
       <c r="A20" s="8">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -3722,7 +3713,7 @@
         <v>15</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>6</v>
@@ -3734,7 +3725,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="81.599999999999994" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="81" x14ac:dyDescent="0.25">
       <c r="A21" s="8">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -3746,7 +3737,7 @@
         <v>15</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>6</v>
@@ -3758,7 +3749,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="61.2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" ht="60.75" x14ac:dyDescent="0.25">
       <c r="A22" s="8">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -3770,7 +3761,7 @@
         <v>15</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>6</v>
@@ -3782,7 +3773,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="61.2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="60.75" x14ac:dyDescent="0.25">
       <c r="A23" s="8">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -3794,7 +3785,7 @@
         <v>15</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>6</v>
@@ -3806,7 +3797,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="61.2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="60.75" x14ac:dyDescent="0.25">
       <c r="A24" s="8">
         <f t="shared" si="0"/>
         <v>22</v>
@@ -3818,7 +3809,7 @@
         <v>15</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>6</v>
@@ -3830,7 +3821,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="61.2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" ht="60.75" x14ac:dyDescent="0.25">
       <c r="A25" s="8">
         <f t="shared" si="0"/>
         <v>23</v>
@@ -3842,7 +3833,7 @@
         <v>15</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>6</v>
@@ -3854,7 +3845,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="61.2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" ht="60.75" x14ac:dyDescent="0.25">
       <c r="A26" s="8">
         <f t="shared" si="0"/>
         <v>24</v>
@@ -3866,7 +3857,7 @@
         <v>15</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>6</v>
@@ -3878,7 +3869,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="40.799999999999997" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" ht="40.5" x14ac:dyDescent="0.25">
       <c r="A27" s="8">
         <f t="shared" si="0"/>
         <v>25</v>
@@ -3890,7 +3881,7 @@
         <v>15</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>6</v>
@@ -3902,7 +3893,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="40.799999999999997" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" ht="40.5" x14ac:dyDescent="0.25">
       <c r="A28" s="8">
         <f t="shared" si="0"/>
         <v>26</v>
@@ -3914,7 +3905,7 @@
         <v>15</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>6</v>
@@ -3926,7 +3917,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="40.799999999999997" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" ht="40.5" x14ac:dyDescent="0.25">
       <c r="A29" s="8">
         <f t="shared" si="0"/>
         <v>27</v>
@@ -3938,7 +3929,7 @@
         <v>15</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>6</v>
@@ -3950,7 +3941,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="61.2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" ht="60.75" x14ac:dyDescent="0.25">
       <c r="A30" s="8">
         <v>29</v>
       </c>
@@ -3961,7 +3952,7 @@
         <v>15</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>6</v>
@@ -3973,7 +3964,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="61.2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" ht="60.75" x14ac:dyDescent="0.25">
       <c r="A31" s="8">
         <v>30</v>
       </c>
@@ -3984,7 +3975,7 @@
         <v>15</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>6</v>
@@ -3996,7 +3987,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="61.2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" ht="60.75" x14ac:dyDescent="0.25">
       <c r="A32" s="8">
         <v>31</v>
       </c>
@@ -4007,7 +3998,7 @@
         <v>15</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>6</v>
@@ -4019,7 +4010,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="142.80000000000001" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" ht="141.75" x14ac:dyDescent="0.25">
       <c r="A33" s="8">
         <v>32</v>
       </c>
@@ -4033,7 +4024,7 @@
         <v>17</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F33" s="3" t="s">
         <v>7</v>
@@ -4042,7 +4033,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="122.4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" ht="121.5" x14ac:dyDescent="0.25">
       <c r="A34" s="3">
         <f t="shared" si="0"/>
         <v>33</v>
@@ -4054,10 +4045,10 @@
         <v>15</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F34" s="3" t="s">
         <v>7</v>
@@ -4066,7 +4057,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="61.2" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" ht="81" x14ac:dyDescent="0.25">
       <c r="A35" s="3">
         <f t="shared" si="0"/>
         <v>34</v>
@@ -4084,13 +4075,13 @@
         <v>6</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G35" s="3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="225.6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" ht="222.75" x14ac:dyDescent="0.25">
       <c r="A36" s="3">
         <f t="shared" si="0"/>
         <v>35</v>
@@ -4102,7 +4093,7 @@
         <v>15</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E36" s="3" t="s">
         <v>6</v>
@@ -4114,7 +4105,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="61.2" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" ht="81" x14ac:dyDescent="0.25">
       <c r="A37" s="3">
         <f t="shared" si="0"/>
         <v>36</v>
@@ -4138,7 +4129,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="40.799999999999997" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" ht="40.5" x14ac:dyDescent="0.25">
       <c r="A38" s="3">
         <f t="shared" ref="A38:A40" si="1">A37+1</f>
         <v>37</v>
@@ -4150,7 +4141,7 @@
         <v>15</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E38" s="3" t="s">
         <v>6</v>
@@ -4162,7 +4153,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="39" spans="1:8" ht="40.799999999999997" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" ht="60.75" x14ac:dyDescent="0.25">
       <c r="A39" s="3">
         <f t="shared" si="1"/>
         <v>38</v>
@@ -4174,7 +4165,7 @@
         <v>15</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E39" s="3" t="s">
         <v>6</v>
@@ -4186,7 +4177,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="40.799999999999997" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" ht="60.75" x14ac:dyDescent="0.25">
       <c r="A40" s="3">
         <f t="shared" si="1"/>
         <v>39</v>
@@ -4198,7 +4189,7 @@
         <v>15</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>6</v>
@@ -4210,7 +4201,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="41" spans="1:8" ht="40.799999999999997" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" ht="60.75" x14ac:dyDescent="0.25">
       <c r="A41" s="3">
         <f t="shared" ref="A41:A76" si="2">A40+1</f>
         <v>40</v>
@@ -4222,7 +4213,7 @@
         <v>15</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E41" s="3" t="s">
         <v>6</v>
@@ -4234,7 +4225,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="61.2" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" ht="60.75" x14ac:dyDescent="0.25">
       <c r="A42" s="3">
         <f t="shared" si="2"/>
         <v>41</v>
@@ -4246,19 +4237,19 @@
         <v>15</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="F42" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="F42" s="10" t="s">
         <v>7</v>
       </c>
       <c r="G42" s="3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="43" spans="1:8" ht="40.799999999999997" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" ht="40.5" x14ac:dyDescent="0.25">
       <c r="A43" s="3">
         <f t="shared" si="2"/>
         <v>42</v>
@@ -4270,10 +4261,10 @@
         <v>15</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F43" s="3" t="s">
         <v>7</v>
@@ -4281,11 +4272,9 @@
       <c r="G43" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="H43" s="9" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" ht="61.2" x14ac:dyDescent="0.25">
+      <c r="H43" s="19"/>
+    </row>
+    <row r="44" spans="1:8" ht="60.75" x14ac:dyDescent="0.25">
       <c r="A44" s="3">
         <f t="shared" si="2"/>
         <v>43</v>
@@ -4297,10 +4286,10 @@
         <v>15</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F44" s="3" t="s">
         <v>7</v>
@@ -4309,7 +4298,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="45" spans="1:8" ht="61.2" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" ht="60.75" x14ac:dyDescent="0.25">
       <c r="A45" s="3">
         <f t="shared" si="2"/>
         <v>44</v>
@@ -4321,10 +4310,10 @@
         <v>15</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F45" s="3" t="s">
         <v>7</v>
@@ -4333,7 +4322,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="61.2" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" ht="60.75" x14ac:dyDescent="0.25">
       <c r="A46" s="3">
         <f t="shared" si="2"/>
         <v>45</v>
@@ -4345,10 +4334,10 @@
         <v>15</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F46" s="3" t="s">
         <v>7</v>
@@ -4357,7 +4346,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="40.799999999999997" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" ht="40.5" x14ac:dyDescent="0.25">
       <c r="A47" s="3">
         <f t="shared" si="2"/>
         <v>46</v>
@@ -4369,7 +4358,7 @@
         <v>15</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>6</v>
@@ -4381,7 +4370,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="48" spans="1:8" ht="40.799999999999997" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" ht="40.5" x14ac:dyDescent="0.25">
       <c r="A48" s="3">
         <f t="shared" si="2"/>
         <v>47</v>
@@ -4393,7 +4382,7 @@
         <v>15</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E48" s="3" t="s">
         <v>6</v>
@@ -4405,7 +4394,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="49" spans="1:7" ht="40.799999999999997" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" ht="40.5" x14ac:dyDescent="0.25">
       <c r="A49" s="3">
         <f t="shared" si="2"/>
         <v>48</v>
@@ -4417,7 +4406,7 @@
         <v>15</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>6</v>
@@ -4429,7 +4418,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="50" spans="1:7" ht="40.799999999999997" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" ht="40.5" x14ac:dyDescent="0.25">
       <c r="A50" s="3">
         <f t="shared" si="2"/>
         <v>49</v>
@@ -4441,7 +4430,7 @@
         <v>15</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E50" s="3" t="s">
         <v>6</v>
@@ -4453,7 +4442,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="51" spans="1:7" ht="40.799999999999997" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7" ht="40.5" x14ac:dyDescent="0.25">
       <c r="A51" s="3">
         <f t="shared" si="2"/>
         <v>50</v>
@@ -4465,7 +4454,7 @@
         <v>15</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E51" s="3" t="s">
         <v>6</v>
@@ -4477,7 +4466,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="52" spans="1:7" ht="40.799999999999997" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7" ht="40.5" x14ac:dyDescent="0.25">
       <c r="A52" s="3">
         <f t="shared" si="2"/>
         <v>51</v>
@@ -4489,7 +4478,7 @@
         <v>15</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E52" s="3" t="s">
         <v>6</v>
@@ -4501,7 +4490,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="53" spans="1:7" ht="40.799999999999997" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7" ht="40.5" x14ac:dyDescent="0.25">
       <c r="A53" s="3">
         <f t="shared" si="2"/>
         <v>52</v>
@@ -4510,10 +4499,10 @@
         <v>12</v>
       </c>
       <c r="C53" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D53" s="3" t="s">
         <v>69</v>
-      </c>
-      <c r="D53" s="3" t="s">
-        <v>70</v>
       </c>
       <c r="E53" s="3" t="s">
         <v>6</v>
@@ -4525,7 +4514,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="54" spans="1:7" ht="61.8" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7" ht="81" x14ac:dyDescent="0.25">
       <c r="A54" s="3">
         <f t="shared" si="2"/>
         <v>53</v>
@@ -4537,7 +4526,7 @@
         <v>13</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E54" s="3" t="s">
         <v>6</v>
@@ -4875,21 +4864,21 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6A548FC-132A-4BCF-B26C-A9E84109E40A}">
   <dimension ref="A1:D11"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="30" customWidth="1"/>
-    <col min="3" max="3" width="34.69921875" customWidth="1"/>
+    <col min="3" max="3" width="34.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="20.399999999999999" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="21" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
         <v>11</v>
       </c>
       <c r="B1" s="17"/>
       <c r="C1" s="18"/>
-      <c r="D1" s="19"/>
-    </row>
-    <row r="2" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="D1" s="11"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -4899,62 +4888,62 @@
       <c r="C2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="19"/>
+      <c r="D2" s="11"/>
     </row>
     <row r="3" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D3" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="D3" s="19" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="40.799999999999997" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:4" ht="42" x14ac:dyDescent="0.25">
       <c r="A4" s="6">
         <f>A3+1</f>
         <v>2</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C4" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="C4" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="D4" s="19"/>
-    </row>
-    <row r="5" spans="1:4" ht="61.2" x14ac:dyDescent="0.25">
+      <c r="D4" s="11"/>
+    </row>
+    <row r="5" spans="1:4" ht="63" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
         <f>A4+1</f>
         <v>3</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C5" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="C5" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="D5" s="19"/>
-    </row>
-    <row r="6" spans="1:4" ht="61.2" x14ac:dyDescent="0.25">
+      <c r="D5" s="11"/>
+    </row>
+    <row r="6" spans="1:4" ht="63" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
         <f>A5+1</f>
         <v>4</v>
       </c>
       <c r="B6" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="C6" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="C6" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="D6" s="19"/>
-    </row>
-    <row r="7" spans="1:4" ht="40.799999999999997" x14ac:dyDescent="0.25">
+      <c r="D6" s="11"/>
+    </row>
+    <row r="7" spans="1:4" ht="42" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
         <v>5</v>
       </c>
@@ -4962,25 +4951,25 @@
         <v>12</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="20.399999999999999" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="21" x14ac:dyDescent="0.25">
       <c r="A8" s="4"/>
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
     </row>
-    <row r="9" spans="1:4" ht="20.399999999999999" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" ht="21" x14ac:dyDescent="0.25">
       <c r="A9" s="4"/>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
     </row>
-    <row r="10" spans="1:4" ht="20.399999999999999" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" ht="21" x14ac:dyDescent="0.25">
       <c r="A10" s="4"/>
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
     </row>
-    <row r="11" spans="1:4" ht="20.399999999999999" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" ht="21" x14ac:dyDescent="0.25">
       <c r="A11" s="4"/>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
